--- a/2026/SALTA 1167/Febrero/SALTA1167-Febrero.xlsx
+++ b/2026/SALTA 1167/Febrero/SALTA1167-Febrero.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE11F7C-8646-48E8-9336-80FF45083F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C04307-AD12-430C-8FF2-AF7150DA6399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,9 +78,6 @@
     <t>HORARIOS DE ATENCION: LUNES A VIERNES</t>
   </si>
   <si>
-    <t>10 A 16HS - EMERGENCIAS 24HS</t>
-  </si>
-  <si>
     <t>Deuda o Saldo a favor</t>
   </si>
   <si>
@@ -485,6 +482,9 @@
   </si>
   <si>
     <t>Insumos de limpieza</t>
+  </si>
+  <si>
+    <t>10 A 15HS - EMERGENCIAS 24HS</t>
   </si>
 </sst>
 </file>
@@ -1515,141 +1515,6 @@
     <xf numFmtId="44" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1657,6 +1522,141 @@
     <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2041,7 +2041,7 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="B1" s="51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C1" s="51"/>
       <c r="D1" s="51"/>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14"/>
-      <c r="B3" s="223" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="223"/>
-      <c r="D3" s="223"/>
-      <c r="E3" s="224"/>
+      <c r="B3" s="224" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="224"/>
+      <c r="D3" s="224"/>
+      <c r="E3" s="225"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="70" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="53" t="s">
@@ -2091,59 +2091,59 @@
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="226" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="226"/>
+      <c r="B8" s="227" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="227"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="226"/>
-      <c r="C9" s="226"/>
+      <c r="B9" s="227"/>
+      <c r="C9" s="227"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="226"/>
-      <c r="C10" s="226"/>
+      <c r="B10" s="227"/>
+      <c r="C10" s="227"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="225" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="225"/>
-      <c r="C13" s="225"/>
-      <c r="D13" s="225"/>
-      <c r="E13" s="225"/>
+      <c r="A13" s="226" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="226"/>
+      <c r="C13" s="226"/>
+      <c r="D13" s="226"/>
+      <c r="E13" s="226"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="225"/>
-      <c r="B14" s="225"/>
-      <c r="C14" s="225"/>
-      <c r="D14" s="225"/>
-      <c r="E14" s="225"/>
+      <c r="A14" s="226"/>
+      <c r="B14" s="226"/>
+      <c r="C14" s="226"/>
+      <c r="D14" s="226"/>
+      <c r="E14" s="226"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="225"/>
-      <c r="B15" s="225"/>
-      <c r="C15" s="225"/>
-      <c r="D15" s="225"/>
-      <c r="E15" s="225"/>
+      <c r="A15" s="226"/>
+      <c r="B15" s="226"/>
+      <c r="C15" s="226"/>
+      <c r="D15" s="226"/>
+      <c r="E15" s="226"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="225"/>
-      <c r="B16" s="225"/>
-      <c r="C16" s="225"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="225"/>
+      <c r="A16" s="226"/>
+      <c r="B16" s="226"/>
+      <c r="C16" s="226"/>
+      <c r="D16" s="226"/>
+      <c r="E16" s="226"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -2152,7 +2152,7 @@
     <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="11"/>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -2169,26 +2169,26 @@
       <c r="E21" s="102"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="216" t="s">
-        <v>119</v>
-      </c>
-      <c r="B22" s="217"/>
+      <c r="A22" s="222" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="223"/>
       <c r="C22" s="39"/>
       <c r="D22" s="118">
         <v>465000.72</v>
       </c>
       <c r="E22" s="111" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H22" s="91"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="216" t="s">
-        <v>150</v>
-      </c>
-      <c r="B23" s="217"/>
+      <c r="A23" s="222" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="223"/>
       <c r="C23" s="39"/>
-      <c r="D23" s="261">
+      <c r="D23" s="216">
         <v>84638.61</v>
       </c>
       <c r="E23" s="111"/>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -2216,16 +2216,16 @@
       <c r="E25" s="131"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="216" t="s">
-        <v>127</v>
-      </c>
-      <c r="B26" s="217"/>
+      <c r="A26" s="222" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="223"/>
       <c r="C26" s="41"/>
       <c r="D26" s="182">
         <v>74584</v>
       </c>
       <c r="E26" s="104" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -2251,31 +2251,31 @@
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="262">
+      <c r="D29" s="217">
         <v>275382.28999999998</v>
       </c>
       <c r="E29" s="111"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="262">
+      <c r="D30" s="217">
         <v>5432.38</v>
       </c>
       <c r="E30" s="111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B31" s="128"/>
       <c r="C31" s="5"/>
@@ -2283,25 +2283,25 @@
         <v>275296.83</v>
       </c>
       <c r="E31" s="111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="221" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="222"/>
+      <c r="A32" s="220" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="221"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="262">
+      <c r="D32" s="217">
         <v>174848.74</v>
       </c>
       <c r="E32" s="111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="114" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B33" s="110"/>
       <c r="C33" s="5"/>
@@ -2309,7 +2309,7 @@
         <v>22064.59</v>
       </c>
       <c r="E33" s="111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2332,30 +2332,30 @@
       <c r="E35" s="108"/>
     </row>
     <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="216" t="s">
-        <v>121</v>
-      </c>
-      <c r="B36" s="217"/>
+      <c r="A36" s="222" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="223"/>
       <c r="C36" s="5"/>
       <c r="D36" s="112">
         <v>75000</v>
       </c>
       <c r="E36" s="113" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="264"/>
+      <c r="A37" s="219"/>
       <c r="B37" s="130"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="263">
+      <c r="D37" s="218">
         <v>4800</v>
       </c>
       <c r="E37" s="113"/>
     </row>
     <row r="38" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="129" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B38" s="130"/>
       <c r="C38" s="5"/>
@@ -2363,7 +2363,7 @@
         <v>103200</v>
       </c>
       <c r="E38" s="113" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -2388,19 +2388,19 @@
       <c r="E40" s="102"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="216" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" s="217"/>
+      <c r="A41" s="222" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="223"/>
       <c r="C41" s="39"/>
       <c r="D41" s="118">
         <v>150000</v>
       </c>
       <c r="E41" s="135" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2433,7 +2433,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2472,7 +2472,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B49" s="22"/>
       <c r="C49" s="22"/>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="4"/>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
@@ -2528,8 +2528,8 @@
       <c r="E55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="220"/>
-      <c r="B56" s="220"/>
+      <c r="A56" s="230"/>
+      <c r="B56" s="230"/>
       <c r="C56" s="5"/>
       <c r="D56" s="112"/>
       <c r="E56" s="74"/>
@@ -2562,7 +2562,7 @@
     <row r="61" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B62" s="22"/>
       <c r="C62" s="22"/>
@@ -2572,7 +2572,7 @@
     <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B64" s="8"/>
       <c r="C64" s="4"/>
@@ -2585,7 +2585,7 @@
     <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B66" s="72">
         <f>E51</f>
@@ -2594,7 +2594,7 @@
     </row>
     <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B67" s="72">
         <f>E51-E49</f>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="71" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B68" s="72">
         <f>E64-E62</f>
@@ -2612,7 +2612,7 @@
     </row>
     <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="71" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B69" s="72">
         <f>E64</f>
@@ -2626,7 +2626,7 @@
     </row>
     <row r="72" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="93" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B72" s="148">
         <v>-991192.32999999973</v>
@@ -2636,7 +2636,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B73" s="98">
         <f>-B67</f>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B74" s="98">
         <f>B93</f>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="41" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B75" s="99">
         <f>PRORRATEO!G36-B83</f>
@@ -2663,19 +2663,19 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B76" s="99"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B77" s="124"/>
     </row>
     <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="96" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B78" s="97">
         <f>SUM(B72:C77)</f>
@@ -2690,7 +2690,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="93" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B80" s="148">
         <v>2000000</v>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B81" s="98">
         <f>-B68</f>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B82" s="98">
         <f>B101</f>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B83" s="99">
         <v>0</v>
@@ -2728,13 +2728,13 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B84" s="124"/>
     </row>
     <row r="85" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="96" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B85" s="97">
         <f>SUM(B80:C84)</f>
@@ -2751,16 +2751,16 @@
     </row>
     <row r="88" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A89" s="219" t="s">
-        <v>19</v>
-      </c>
-      <c r="B89" s="219"/>
-      <c r="C89" s="219"/>
+      <c r="A89" s="229" t="s">
+        <v>18</v>
+      </c>
+      <c r="B89" s="229"/>
+      <c r="C89" s="229"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A90" s="219"/>
-      <c r="B90" s="219"/>
-      <c r="C90" s="219"/>
+      <c r="A90" s="229"/>
+      <c r="B90" s="229"/>
+      <c r="C90" s="229"/>
     </row>
     <row r="91" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="88"/>
@@ -2790,35 +2790,40 @@
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="218"/>
-      <c r="B95" s="218"/>
-      <c r="C95" s="218"/>
-      <c r="D95" s="218"/>
-      <c r="E95" s="218"/>
+      <c r="A95" s="228"/>
+      <c r="B95" s="228"/>
+      <c r="C95" s="228"/>
+      <c r="D95" s="228"/>
+      <c r="E95" s="228"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A96" s="218"/>
-      <c r="B96" s="218"/>
-      <c r="C96" s="218"/>
-      <c r="D96" s="218"/>
-      <c r="E96" s="218"/>
+      <c r="A96" s="228"/>
+      <c r="B96" s="228"/>
+      <c r="C96" s="228"/>
+      <c r="D96" s="228"/>
+      <c r="E96" s="228"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="218"/>
-      <c r="B97" s="218"/>
-      <c r="C97" s="218"/>
-      <c r="D97" s="218"/>
-      <c r="E97" s="218"/>
+      <c r="A97" s="228"/>
+      <c r="B97" s="228"/>
+      <c r="C97" s="228"/>
+      <c r="D97" s="228"/>
+      <c r="E97" s="228"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="218"/>
-      <c r="B98" s="218"/>
-      <c r="C98" s="218"/>
-      <c r="D98" s="218"/>
-      <c r="E98" s="218"/>
+      <c r="A98" s="228"/>
+      <c r="B98" s="228"/>
+      <c r="C98" s="228"/>
+      <c r="D98" s="228"/>
+      <c r="E98" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A95:E98"/>
+    <mergeCell ref="A89:C90"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2826,11 +2831,6 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A95:E98"/>
-    <mergeCell ref="A89:C90"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2868,16 +2868,16 @@
       <c r="B1" s="150"/>
       <c r="C1" s="151"/>
       <c r="D1" s="151"/>
-      <c r="E1" s="230"/>
-      <c r="F1" s="230"/>
-      <c r="G1" s="230"/>
-      <c r="H1" s="230"/>
-      <c r="I1" s="230"/>
-      <c r="J1" s="230"/>
-      <c r="K1" s="230"/>
-      <c r="L1" s="230"/>
-      <c r="M1" s="230"/>
-      <c r="N1" s="230"/>
+      <c r="E1" s="231"/>
+      <c r="F1" s="231"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
+      <c r="K1" s="231"/>
+      <c r="L1" s="231"/>
+      <c r="M1" s="231"/>
+      <c r="N1" s="231"/>
       <c r="O1" s="150"/>
       <c r="P1" s="152"/>
     </row>
@@ -2887,7 +2887,7 @@
       <c r="C2" s="155"/>
       <c r="D2" s="156"/>
       <c r="E2" s="156" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F2" s="156"/>
       <c r="G2" s="157">
@@ -2897,7 +2897,7 @@
       <c r="I2" s="156"/>
       <c r="J2" s="158"/>
       <c r="K2" s="156" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L2" s="159">
         <v>2000000</v>
@@ -2928,219 +2928,219 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="240" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="241"/>
-      <c r="C4" s="241"/>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="M4" s="241"/>
-      <c r="N4" s="241"/>
-      <c r="O4" s="241"/>
-      <c r="P4" s="242"/>
+      <c r="A4" s="243" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="244"/>
+      <c r="C4" s="244"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="M4" s="244"/>
+      <c r="N4" s="244"/>
+      <c r="O4" s="244"/>
+      <c r="P4" s="245"/>
       <c r="Q4" s="20"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="243"/>
-      <c r="B5" s="244"/>
-      <c r="C5" s="244"/>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="M5" s="244"/>
-      <c r="N5" s="244"/>
-      <c r="O5" s="244"/>
-      <c r="P5" s="245"/>
+      <c r="A5" s="246"/>
+      <c r="B5" s="247"/>
+      <c r="C5" s="247"/>
+      <c r="D5" s="247"/>
+      <c r="E5" s="247"/>
+      <c r="F5" s="247"/>
+      <c r="G5" s="247"/>
+      <c r="H5" s="247"/>
+      <c r="I5" s="247"/>
+      <c r="J5" s="247"/>
+      <c r="K5" s="247"/>
+      <c r="L5" s="247"/>
+      <c r="M5" s="247"/>
+      <c r="N5" s="247"/>
+      <c r="O5" s="247"/>
+      <c r="P5" s="248"/>
       <c r="Q5" s="20"/>
     </row>
     <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="243"/>
-      <c r="B6" s="244"/>
-      <c r="C6" s="244"/>
-      <c r="D6" s="244"/>
-      <c r="E6" s="244"/>
-      <c r="F6" s="244"/>
-      <c r="G6" s="244"/>
-      <c r="H6" s="244"/>
-      <c r="I6" s="244"/>
-      <c r="J6" s="244"/>
-      <c r="K6" s="244"/>
-      <c r="L6" s="244"/>
-      <c r="M6" s="244"/>
-      <c r="N6" s="244"/>
-      <c r="O6" s="244"/>
-      <c r="P6" s="245"/>
+      <c r="A6" s="246"/>
+      <c r="B6" s="247"/>
+      <c r="C6" s="247"/>
+      <c r="D6" s="247"/>
+      <c r="E6" s="247"/>
+      <c r="F6" s="247"/>
+      <c r="G6" s="247"/>
+      <c r="H6" s="247"/>
+      <c r="I6" s="247"/>
+      <c r="J6" s="247"/>
+      <c r="K6" s="247"/>
+      <c r="L6" s="247"/>
+      <c r="M6" s="247"/>
+      <c r="N6" s="247"/>
+      <c r="O6" s="247"/>
+      <c r="P6" s="248"/>
       <c r="Q6" s="20"/>
     </row>
     <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="243"/>
-      <c r="B7" s="244"/>
-      <c r="C7" s="244"/>
-      <c r="D7" s="244"/>
-      <c r="E7" s="244"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="244"/>
-      <c r="I7" s="244"/>
-      <c r="J7" s="244"/>
-      <c r="K7" s="244"/>
-      <c r="L7" s="244"/>
-      <c r="M7" s="244"/>
-      <c r="N7" s="244"/>
-      <c r="O7" s="244"/>
-      <c r="P7" s="245"/>
+      <c r="A7" s="246"/>
+      <c r="B7" s="247"/>
+      <c r="C7" s="247"/>
+      <c r="D7" s="247"/>
+      <c r="E7" s="247"/>
+      <c r="F7" s="247"/>
+      <c r="G7" s="247"/>
+      <c r="H7" s="247"/>
+      <c r="I7" s="247"/>
+      <c r="J7" s="247"/>
+      <c r="K7" s="247"/>
+      <c r="L7" s="247"/>
+      <c r="M7" s="247"/>
+      <c r="N7" s="247"/>
+      <c r="O7" s="247"/>
+      <c r="P7" s="248"/>
       <c r="Q7" s="20"/>
     </row>
     <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="246"/>
-      <c r="B8" s="247"/>
-      <c r="C8" s="247"/>
-      <c r="D8" s="247"/>
-      <c r="E8" s="247"/>
-      <c r="F8" s="247"/>
-      <c r="G8" s="247"/>
-      <c r="H8" s="247"/>
-      <c r="I8" s="247"/>
-      <c r="J8" s="247"/>
-      <c r="K8" s="247"/>
-      <c r="L8" s="247"/>
-      <c r="M8" s="247"/>
-      <c r="N8" s="247"/>
-      <c r="O8" s="247"/>
-      <c r="P8" s="248"/>
+      <c r="A8" s="249"/>
+      <c r="B8" s="250"/>
+      <c r="C8" s="250"/>
+      <c r="D8" s="250"/>
+      <c r="E8" s="250"/>
+      <c r="F8" s="250"/>
+      <c r="G8" s="250"/>
+      <c r="H8" s="250"/>
+      <c r="I8" s="250"/>
+      <c r="J8" s="250"/>
+      <c r="K8" s="250"/>
+      <c r="L8" s="250"/>
+      <c r="M8" s="250"/>
+      <c r="N8" s="250"/>
+      <c r="O8" s="250"/>
+      <c r="P8" s="251"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="251" t="s">
-        <v>145</v>
-      </c>
-      <c r="B9" s="252"/>
-      <c r="C9" s="252"/>
-      <c r="D9" s="252"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
-      <c r="H9" s="252"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="252"/>
-      <c r="K9" s="252"/>
-      <c r="L9" s="252"/>
-      <c r="M9" s="252"/>
-      <c r="N9" s="252"/>
-      <c r="O9" s="252"/>
-      <c r="P9" s="252"/>
+      <c r="A9" s="254" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="255"/>
+      <c r="C9" s="255"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
+      <c r="M9" s="255"/>
+      <c r="N9" s="255"/>
+      <c r="O9" s="255"/>
+      <c r="P9" s="255"/>
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="253" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="253"/>
-      <c r="C10" s="253"/>
-      <c r="D10" s="253"/>
-      <c r="E10" s="253"/>
-      <c r="F10" s="253"/>
-      <c r="G10" s="253"/>
-      <c r="H10" s="253"/>
-      <c r="I10" s="253"/>
-      <c r="J10" s="253"/>
-      <c r="K10" s="253"/>
-      <c r="L10" s="253"/>
-      <c r="M10" s="253"/>
-      <c r="N10" s="253"/>
-      <c r="O10" s="253"/>
-      <c r="P10" s="253"/>
+      <c r="A10" s="256" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="256"/>
+      <c r="C10" s="256"/>
+      <c r="D10" s="256"/>
+      <c r="E10" s="256"/>
+      <c r="F10" s="256"/>
+      <c r="G10" s="256"/>
+      <c r="H10" s="256"/>
+      <c r="I10" s="256"/>
+      <c r="J10" s="256"/>
+      <c r="K10" s="256"/>
+      <c r="L10" s="256"/>
+      <c r="M10" s="256"/>
+      <c r="N10" s="256"/>
+      <c r="O10" s="256"/>
+      <c r="P10" s="256"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="227" t="s">
+      <c r="A11" s="236" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="125"/>
-      <c r="C11" s="227" t="s">
+      <c r="C11" s="236" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="227" t="s">
+      <c r="D11" s="236" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="227" t="s">
+      <c r="E11" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="231" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="227" t="s">
+      <c r="F11" s="232" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="236" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="235" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="231" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="231" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="231" t="s">
+      <c r="H11" s="238" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="232" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="232" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="232" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" s="241" t="s">
         <v>98</v>
       </c>
-      <c r="L11" s="238" t="s">
-        <v>99</v>
-      </c>
-      <c r="M11" s="231" t="s">
-        <v>83</v>
+      <c r="M11" s="232" t="s">
+        <v>82</v>
       </c>
       <c r="N11" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="233" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" s="234" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="249" t="s">
-        <v>20</v>
+      <c r="P11" s="252" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="229"/>
+      <c r="A12" s="237"/>
       <c r="B12" s="126"/>
-      <c r="C12" s="229"/>
-      <c r="D12" s="228"/>
-      <c r="E12" s="229"/>
-      <c r="F12" s="232"/>
-      <c r="G12" s="229"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="232"/>
-      <c r="J12" s="237"/>
-      <c r="K12" s="232"/>
-      <c r="L12" s="239"/>
-      <c r="M12" s="232"/>
+      <c r="C12" s="237"/>
+      <c r="D12" s="257"/>
+      <c r="E12" s="237"/>
+      <c r="F12" s="233"/>
+      <c r="G12" s="237"/>
+      <c r="H12" s="239"/>
+      <c r="I12" s="233"/>
+      <c r="J12" s="240"/>
+      <c r="K12" s="233"/>
+      <c r="L12" s="242"/>
+      <c r="M12" s="233"/>
       <c r="N12" s="43" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="O12" s="234"/>
-      <c r="P12" s="250"/>
+      <c r="O12" s="235"/>
+      <c r="P12" s="253"/>
     </row>
     <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="46">
         <v>1</v>
       </c>
       <c r="B13" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="46" t="s">
         <v>30</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>31</v>
       </c>
       <c r="D13" s="46"/>
       <c r="E13" s="55">
@@ -3198,10 +3198,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="46" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>33</v>
       </c>
       <c r="D14" s="47"/>
       <c r="E14" s="55">
@@ -3260,13 +3260,13 @@
         <v>3</v>
       </c>
       <c r="B15" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="46" t="s">
-        <v>35</v>
-      </c>
       <c r="D15" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E15" s="55">
         <v>5.4</v>
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="46" t="s">
-        <v>37</v>
-      </c>
       <c r="D16" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" s="55">
         <v>6.6</v>
@@ -3388,13 +3388,13 @@
         <v>5</v>
       </c>
       <c r="B17" s="165" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="165" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="165" t="s">
-        <v>39</v>
-      </c>
       <c r="D17" s="165" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E17" s="166">
         <v>6.6</v>
@@ -3447,7 +3447,7 @@
         <v>0.05</v>
       </c>
       <c r="R17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -3455,13 +3455,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="46" t="s">
-        <v>41</v>
-      </c>
       <c r="D18" s="46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E18" s="55">
         <v>5.4</v>
@@ -3519,13 +3519,13 @@
         <v>7</v>
       </c>
       <c r="B19" s="202" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="202" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="202" t="s">
-        <v>43</v>
-      </c>
       <c r="D19" s="202" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" s="204">
         <v>5.4</v>
@@ -3580,13 +3580,13 @@
         <v>8</v>
       </c>
       <c r="B20" s="202" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="202" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="202" t="s">
-        <v>45</v>
-      </c>
       <c r="D20" s="203" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E20" s="204">
         <v>6.6</v>
@@ -3644,13 +3644,13 @@
         <v>9</v>
       </c>
       <c r="B21" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="46" t="s">
-        <v>47</v>
-      </c>
       <c r="D21" s="47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" s="55">
         <v>6.6</v>
@@ -3708,13 +3708,13 @@
         <v>10</v>
       </c>
       <c r="B22" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="46" t="s">
-        <v>49</v>
-      </c>
       <c r="D22" s="47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" s="55">
         <v>5.4</v>
@@ -3772,10 +3772,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="46" t="s">
         <v>50</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>51</v>
       </c>
       <c r="D23" s="47"/>
       <c r="E23" s="55">
@@ -3829,7 +3829,7 @@
         <v>0.10999999999999999</v>
       </c>
       <c r="R23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -3837,13 +3837,13 @@
         <v>12</v>
       </c>
       <c r="B24" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="46" t="s">
-        <v>53</v>
-      </c>
       <c r="D24" s="47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E24" s="55">
         <v>6.6</v>
@@ -3901,13 +3901,13 @@
         <v>13</v>
       </c>
       <c r="B25" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="46" t="s">
-        <v>55</v>
-      </c>
       <c r="D25" s="47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E25" s="55">
         <v>6.6</v>
@@ -3964,10 +3964,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="46" t="s">
         <v>56</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>57</v>
       </c>
       <c r="D26" s="47"/>
       <c r="E26" s="55">
@@ -4026,10 +4026,10 @@
         <v>15</v>
       </c>
       <c r="B27" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="46" t="s">
         <v>58</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>59</v>
       </c>
       <c r="D27" s="47"/>
       <c r="E27" s="55">
@@ -4088,13 +4088,13 @@
         <v>16</v>
       </c>
       <c r="B28" s="46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" s="46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E28" s="55">
         <v>0.7</v>
@@ -4152,10 +4152,10 @@
         <v>17</v>
       </c>
       <c r="B29" s="46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" s="47"/>
       <c r="E29" s="55">
@@ -4214,10 +4214,10 @@
         <v>18</v>
       </c>
       <c r="B30" s="46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30" s="92"/>
       <c r="E30" s="55">
@@ -4276,10 +4276,10 @@
         <v>19</v>
       </c>
       <c r="B31" s="165" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="165" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="201"/>
       <c r="E31" s="166">
@@ -4334,13 +4334,13 @@
         <v>20</v>
       </c>
       <c r="B32" s="62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E32" s="55">
         <v>0.6</v>
@@ -4395,13 +4395,13 @@
         <v>21</v>
       </c>
       <c r="B33" s="62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33" s="48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E33" s="55">
         <v>0.3</v>
@@ -4456,10 +4456,10 @@
         <v>22</v>
       </c>
       <c r="B34" s="63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D34" s="47"/>
       <c r="E34" s="55">
@@ -4515,13 +4515,13 @@
         <v>23</v>
       </c>
       <c r="B35" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="65" t="s">
-        <v>68</v>
-      </c>
       <c r="D35" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E35" s="55">
         <v>0.3</v>
@@ -4628,94 +4628,99 @@
     </row>
     <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="218" t="str">
+      <c r="C39" s="228" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="218"/>
-      <c r="E39" s="218"/>
-      <c r="F39" s="218"/>
-      <c r="G39" s="218"/>
-      <c r="H39" s="218"/>
-      <c r="I39" s="218"/>
-      <c r="J39" s="218"/>
-      <c r="K39" s="218"/>
-      <c r="L39" s="218"/>
-      <c r="M39" s="218"/>
-      <c r="N39" s="218"/>
+      <c r="D39" s="228"/>
+      <c r="E39" s="228"/>
+      <c r="F39" s="228"/>
+      <c r="G39" s="228"/>
+      <c r="H39" s="228"/>
+      <c r="I39" s="228"/>
+      <c r="J39" s="228"/>
+      <c r="K39" s="228"/>
+      <c r="L39" s="228"/>
+      <c r="M39" s="228"/>
+      <c r="N39" s="228"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="218"/>
-      <c r="D40" s="218"/>
-      <c r="E40" s="218"/>
-      <c r="F40" s="218"/>
-      <c r="G40" s="218"/>
-      <c r="H40" s="218"/>
-      <c r="I40" s="218"/>
-      <c r="J40" s="218"/>
-      <c r="K40" s="218"/>
-      <c r="L40" s="218"/>
-      <c r="M40" s="218"/>
-      <c r="N40" s="218"/>
+      <c r="C40" s="228"/>
+      <c r="D40" s="228"/>
+      <c r="E40" s="228"/>
+      <c r="F40" s="228"/>
+      <c r="G40" s="228"/>
+      <c r="H40" s="228"/>
+      <c r="I40" s="228"/>
+      <c r="J40" s="228"/>
+      <c r="K40" s="228"/>
+      <c r="L40" s="228"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="228"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="218"/>
-      <c r="D41" s="218"/>
-      <c r="E41" s="218"/>
-      <c r="F41" s="218"/>
-      <c r="G41" s="218"/>
-      <c r="H41" s="218"/>
-      <c r="I41" s="218"/>
-      <c r="J41" s="218"/>
-      <c r="K41" s="218"/>
-      <c r="L41" s="218"/>
-      <c r="M41" s="218"/>
-      <c r="N41" s="218"/>
+      <c r="C41" s="228"/>
+      <c r="D41" s="228"/>
+      <c r="E41" s="228"/>
+      <c r="F41" s="228"/>
+      <c r="G41" s="228"/>
+      <c r="H41" s="228"/>
+      <c r="I41" s="228"/>
+      <c r="J41" s="228"/>
+      <c r="K41" s="228"/>
+      <c r="L41" s="228"/>
+      <c r="M41" s="228"/>
+      <c r="N41" s="228"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="218"/>
-      <c r="D42" s="218"/>
-      <c r="E42" s="218"/>
-      <c r="F42" s="218"/>
-      <c r="G42" s="218"/>
-      <c r="H42" s="218"/>
-      <c r="I42" s="218"/>
-      <c r="J42" s="218"/>
-      <c r="K42" s="218"/>
-      <c r="L42" s="218"/>
-      <c r="M42" s="218"/>
-      <c r="N42" s="218"/>
+      <c r="C42" s="228"/>
+      <c r="D42" s="228"/>
+      <c r="E42" s="228"/>
+      <c r="F42" s="228"/>
+      <c r="G42" s="228"/>
+      <c r="H42" s="228"/>
+      <c r="I42" s="228"/>
+      <c r="J42" s="228"/>
+      <c r="K42" s="228"/>
+      <c r="L42" s="228"/>
+      <c r="M42" s="228"/>
+      <c r="N42" s="228"/>
     </row>
     <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="218"/>
-      <c r="D43" s="218"/>
-      <c r="E43" s="218"/>
-      <c r="F43" s="218"/>
-      <c r="G43" s="218"/>
-      <c r="H43" s="218"/>
-      <c r="I43" s="218"/>
-      <c r="J43" s="218"/>
-      <c r="K43" s="218"/>
-      <c r="L43" s="218"/>
-      <c r="M43" s="218"/>
-      <c r="N43" s="218"/>
+      <c r="C43" s="228"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="228"/>
+      <c r="F43" s="228"/>
+      <c r="G43" s="228"/>
+      <c r="H43" s="228"/>
+      <c r="I43" s="228"/>
+      <c r="J43" s="228"/>
+      <c r="K43" s="228"/>
+      <c r="L43" s="228"/>
+      <c r="M43" s="228"/>
+      <c r="N43" s="228"/>
     </row>
     <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="218"/>
-      <c r="D44" s="218"/>
-      <c r="E44" s="218"/>
-      <c r="F44" s="218"/>
-      <c r="G44" s="218"/>
-      <c r="H44" s="218"/>
-      <c r="I44" s="218"/>
-      <c r="J44" s="218"/>
-      <c r="K44" s="218"/>
-      <c r="L44" s="218"/>
-      <c r="M44" s="218"/>
-      <c r="N44" s="218"/>
+      <c r="C44" s="228"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="228"/>
+      <c r="F44" s="228"/>
+      <c r="G44" s="228"/>
+      <c r="H44" s="228"/>
+      <c r="I44" s="228"/>
+      <c r="J44" s="228"/>
+      <c r="K44" s="228"/>
+      <c r="L44" s="228"/>
+      <c r="M44" s="228"/>
+      <c r="N44" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4730,11 +4735,6 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="M11:M12"/>
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4764,48 +4764,48 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="D2" s="254" t="s">
+      <c r="D2" s="258" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="259" t="s">
         <v>129</v>
       </c>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="255" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" s="256"/>
+      <c r="I2" s="260"/>
       <c r="J2" s="2"/>
       <c r="K2" s="138" t="s">
+        <v>90</v>
+      </c>
+      <c r="M2" s="183" t="s">
+        <v>130</v>
+      </c>
+      <c r="O2" s="138" t="s">
         <v>91</v>
-      </c>
-      <c r="M2" s="183" t="s">
-        <v>131</v>
-      </c>
-      <c r="O2" s="138" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="136" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="136" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="136" t="s">
-        <v>85</v>
-      </c>
       <c r="D3" s="136" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" s="136" t="s">
         <v>132</v>
       </c>
-      <c r="E3" s="136" t="s">
+      <c r="F3" s="138" t="s">
         <v>133</v>
       </c>
-      <c r="F3" s="138" t="s">
+      <c r="H3" s="136" t="s">
         <v>134</v>
       </c>
-      <c r="H3" s="136" t="s">
+      <c r="I3" s="184" t="s">
         <v>135</v>
-      </c>
-      <c r="I3" s="184" t="s">
-        <v>136</v>
       </c>
       <c r="K3" s="136"/>
       <c r="M3" s="139"/>
@@ -4816,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="136" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D4" s="185">
         <v>132.44000000000014</v>
@@ -4851,7 +4851,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="136" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D5" s="191">
         <v>107.16000000000004</v>
@@ -4885,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="136" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D6" s="191">
         <v>102.28000000000002</v>
@@ -4920,7 +4920,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="137" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" s="185">
         <v>20.160000000000036</v>
@@ -4955,7 +4955,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="137" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" s="185">
         <v>0</v>
@@ -4990,7 +4990,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="137" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" s="185">
         <v>0</v>
@@ -5025,7 +5025,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" s="185">
         <v>0</v>
@@ -5060,7 +5060,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="137" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" s="185">
         <v>0</v>
@@ -5095,7 +5095,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="136" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" s="191">
         <v>253.12000000000006</v>
@@ -5130,7 +5130,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="137" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" s="185">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" s="185">
         <v>0</v>
@@ -5200,7 +5200,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="136" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D15" s="191">
         <v>281.23999999999978</v>
@@ -5235,7 +5235,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="137" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D16" s="185">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="137" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D17" s="185">
         <v>39.36000000000022</v>
@@ -5305,7 +5305,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" s="185">
         <v>0</v>
@@ -5350,7 +5350,7 @@
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="136"/>
       <c r="C20" s="136" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D20" s="191">
         <f>SUM(D4:D19)</f>
@@ -5388,7 +5388,7 @@
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22" s="136">
         <v>1</v>
@@ -5417,7 +5417,7 @@
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C23" s="136">
         <v>2</v>
@@ -5446,7 +5446,7 @@
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C24" s="136">
         <v>3</v>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C25" s="136">
         <v>4</v>
@@ -5504,7 +5504,7 @@
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" s="136">
         <v>5</v>
@@ -5533,7 +5533,7 @@
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C27" s="136">
         <v>6</v>
@@ -5562,7 +5562,7 @@
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C28" s="136">
         <v>7</v>
@@ -5591,7 +5591,7 @@
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C29" s="136">
         <v>8</v>
@@ -5620,7 +5620,7 @@
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H30" s="138" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I30" s="189">
         <f>SUM(I22:I29)</f>
@@ -5643,10 +5643,10 @@
       <c r="O31" s="140"/>
     </row>
     <row r="32" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D32" s="257" t="s">
-        <v>138</v>
-      </c>
-      <c r="E32" s="258"/>
+      <c r="D32" s="261" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="262"/>
       <c r="F32" s="199">
         <v>237798.9</v>
       </c>
@@ -5692,36 +5692,36 @@
   <sheetData>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="136" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="136" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="136" t="s">
-        <v>85</v>
-      </c>
       <c r="E3" s="138" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="180" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="259" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="180" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" s="255" t="s">
-        <v>92</v>
-      </c>
-      <c r="J3" s="256"/>
+      <c r="J3" s="260"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="136"/>
       <c r="C4" s="136"/>
       <c r="E4" s="136"/>
       <c r="G4" s="139"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="256"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="260"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="136">
         <v>1</v>
       </c>
       <c r="C5" s="136" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" s="140">
         <v>26132.02</v>
@@ -5731,18 +5731,18 @@
         <f>E5</f>
         <v>26132.02</v>
       </c>
-      <c r="I5" s="259">
+      <c r="I5" s="263">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="260"/>
+      <c r="J5" s="264"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="136">
         <v>1</v>
       </c>
       <c r="C6" s="136" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6" s="140">
         <v>12925.66</v>
@@ -5752,18 +5752,18 @@
         <f t="shared" ref="G6:G19" si="0">E6</f>
         <v>12925.66</v>
       </c>
-      <c r="I6" s="259">
+      <c r="I6" s="263">
         <f t="shared" ref="I6:I21" si="1">E6-G6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="260"/>
+      <c r="J6" s="264"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="136">
         <v>1</v>
       </c>
       <c r="C7" s="136" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" s="140">
         <v>10709.96</v>
@@ -5773,18 +5773,18 @@
         <f t="shared" si="0"/>
         <v>10709.96</v>
       </c>
-      <c r="I7" s="259">
+      <c r="I7" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J7" s="260"/>
+      <c r="J7" s="264"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="136">
         <v>2</v>
       </c>
       <c r="C8" s="136" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" s="140">
         <v>5448.33</v>
@@ -5794,18 +5794,18 @@
         <f t="shared" si="0"/>
         <v>5448.33</v>
       </c>
-      <c r="I8" s="259">
+      <c r="I8" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="260"/>
+      <c r="J8" s="264"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="137">
         <v>2</v>
       </c>
       <c r="C9" s="137" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9" s="140">
         <v>2716.04</v>
@@ -5815,18 +5815,18 @@
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I9" s="259">
+      <c r="I9" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="260"/>
+      <c r="J9" s="264"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="137">
         <v>2</v>
       </c>
       <c r="C10" s="137" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10" s="140">
         <v>2716.04</v>
@@ -5836,18 +5836,18 @@
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I10" s="259">
+      <c r="I10" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="260"/>
+      <c r="J10" s="264"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="137">
         <v>2</v>
       </c>
       <c r="C11" s="137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11" s="140">
         <v>2222.21</v>
@@ -5857,18 +5857,18 @@
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I11" s="259">
+      <c r="I11" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="260"/>
+      <c r="J11" s="264"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="137">
         <v>3</v>
       </c>
       <c r="C12" s="137" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E12" s="140">
         <v>2222.21</v>
@@ -5878,18 +5878,18 @@
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I12" s="259">
+      <c r="I12" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="260"/>
+      <c r="J12" s="264"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="136">
         <v>3</v>
       </c>
       <c r="C13" s="136" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" s="140">
         <v>24018.62</v>
@@ -5899,18 +5899,18 @@
         <f t="shared" si="0"/>
         <v>24018.62</v>
       </c>
-      <c r="I13" s="259">
+      <c r="I13" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="260"/>
+      <c r="J13" s="264"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="137">
         <v>3</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E14" s="140">
         <v>2716.04</v>
@@ -5920,18 +5920,18 @@
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I14" s="259">
+      <c r="I14" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="260"/>
+      <c r="J14" s="264"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="137">
         <v>3</v>
       </c>
       <c r="C15" s="137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E15" s="140">
         <v>2222.21</v>
@@ -5941,18 +5941,18 @@
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I15" s="259">
+      <c r="I15" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="260"/>
+      <c r="J15" s="264"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="136">
         <v>4</v>
       </c>
       <c r="C16" s="136" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" s="140">
         <v>36166.800000000003</v>
@@ -5962,18 +5962,18 @@
         <f t="shared" si="0"/>
         <v>36166.800000000003</v>
       </c>
-      <c r="I16" s="259">
+      <c r="I16" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="260"/>
+      <c r="J16" s="264"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="137">
         <v>4</v>
       </c>
       <c r="C17" s="137" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E17" s="140">
         <v>2716.04</v>
@@ -5983,18 +5983,18 @@
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I17" s="259">
+      <c r="I17" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="260"/>
+      <c r="J17" s="264"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="136">
         <v>4</v>
       </c>
       <c r="C18" s="136" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E18" s="140">
         <v>9014.634</v>
@@ -6004,18 +6004,18 @@
         <f t="shared" si="0"/>
         <v>9014.634</v>
       </c>
-      <c r="I18" s="259">
+      <c r="I18" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="260"/>
+      <c r="J18" s="264"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="137">
         <v>4</v>
       </c>
       <c r="C19" s="137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E19" s="140">
         <v>2222.21</v>
@@ -6025,23 +6025,23 @@
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I19" s="259">
+      <c r="I19" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="260"/>
+      <c r="J19" s="264"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="136"/>
       <c r="C20" s="136"/>
       <c r="E20" s="136"/>
       <c r="G20" s="139"/>
-      <c r="I20" s="259"/>
-      <c r="J20" s="260"/>
+      <c r="I20" s="263"/>
+      <c r="J20" s="264"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="173" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C21" s="173"/>
       <c r="D21" s="174"/>
@@ -6054,15 +6054,15 @@
         <f>SUM(G5:G20)</f>
         <v>144169.02399999998</v>
       </c>
-      <c r="I21" s="259">
+      <c r="I21" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="260"/>
+      <c r="J21" s="264"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22" s="136">
         <v>1</v>
@@ -6074,15 +6074,15 @@
         <f>E22</f>
         <v>288.06</v>
       </c>
-      <c r="I22" s="259">
+      <c r="I22" s="263">
         <f t="shared" ref="I22" si="2">E22-G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="260"/>
+      <c r="J22" s="264"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C23" s="136">
         <v>2</v>
@@ -6094,15 +6094,15 @@
         <f t="shared" ref="G23:G29" si="3">E23</f>
         <v>246.91</v>
       </c>
-      <c r="I23" s="259">
+      <c r="I23" s="263">
         <f t="shared" ref="I23:I31" si="4">E23-G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="260"/>
+      <c r="J23" s="264"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C24" s="136">
         <v>3</v>
@@ -6114,15 +6114,15 @@
         <f t="shared" si="3"/>
         <v>246.91</v>
       </c>
-      <c r="I24" s="259">
+      <c r="I24" s="263">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J24" s="260"/>
+      <c r="J24" s="264"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C25" s="136">
         <v>4</v>
@@ -6134,15 +6134,15 @@
         <f t="shared" si="3"/>
         <v>246.91</v>
       </c>
-      <c r="I25" s="259">
+      <c r="I25" s="263">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J25" s="260"/>
+      <c r="J25" s="264"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" s="136">
         <v>5</v>
@@ -6154,15 +6154,15 @@
         <f t="shared" si="3"/>
         <v>246.91</v>
       </c>
-      <c r="I26" s="259">
+      <c r="I26" s="263">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="260"/>
+      <c r="J26" s="264"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C27" s="136">
         <v>6</v>
@@ -6174,15 +6174,15 @@
         <f t="shared" si="3"/>
         <v>123.46</v>
       </c>
-      <c r="I27" s="259">
+      <c r="I27" s="263">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="260"/>
+      <c r="J27" s="264"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C28" s="136">
         <v>7</v>
@@ -6194,15 +6194,15 @@
         <f t="shared" si="3"/>
         <v>123.46</v>
       </c>
-      <c r="I28" s="259">
+      <c r="I28" s="263">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J28" s="260"/>
+      <c r="J28" s="264"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C29" s="136">
         <v>8</v>
@@ -6214,15 +6214,15 @@
         <f t="shared" si="3"/>
         <v>123.46</v>
       </c>
-      <c r="I29" s="259">
+      <c r="I29" s="263">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J29" s="260"/>
+      <c r="J29" s="264"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="178" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C30" s="179"/>
       <c r="D30" s="177"/>
@@ -6235,26 +6235,26 @@
         <f>SUM(G22:G29)</f>
         <v>1646.0800000000002</v>
       </c>
-      <c r="I30" s="259">
+      <c r="I30" s="263">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="260"/>
+      <c r="J30" s="264"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E31" s="144"/>
       <c r="G31" s="141"/>
-      <c r="I31" s="259">
+      <c r="I31" s="263">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J31" s="260"/>
+      <c r="J31" s="264"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E32" s="142"/>
       <c r="G32" s="143"/>
-      <c r="I32" s="259"/>
-      <c r="J32" s="260"/>
+      <c r="I32" s="263"/>
+      <c r="J32" s="264"/>
     </row>
     <row r="33" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E33" s="144">
@@ -6265,14 +6265,29 @@
         <f>G21+G30</f>
         <v>145815.10399999996</v>
       </c>
-      <c r="I33" s="259">
+      <c r="I33" s="263">
         <f>E33-G33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="260"/>
+      <c r="J33" s="264"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -6289,21 +6304,6 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>

--- a/2026/SALTA 1167/Febrero/SALTA1167-Febrero.xlsx
+++ b/2026/SALTA 1167/Febrero/SALTA1167-Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\SALTA 1167\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBF0522-AC54-4A03-8E28-81382972CCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAEAC11-6550-44F7-A905-B7F08ECCDB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,18 +22,10 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -498,16 +490,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -1130,8 +1122,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1154,25 +1146,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1180,15 +1172,15 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1202,7 +1194,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1210,25 +1202,25 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1236,25 +1228,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1263,53 +1255,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="10" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="10" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1318,7 +1310,7 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1328,11 +1320,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1347,10 +1339,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1359,19 +1351,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1386,41 +1378,41 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="12" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="12" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="12" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1430,8 +1422,8 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1442,18 +1434,33 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="12" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1461,6 +1468,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1470,104 +1489,92 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1575,24 +1582,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1668,9 +1660,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1708,9 +1700,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1743,9 +1735,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1778,9 +1787,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1955,21 +1981,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M103"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.54296875" customWidth="1"/>
-    <col min="2" max="2" width="24.6328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6328125" customWidth="1"/>
-    <col min="5" max="5" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.36328125" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="B1" s="51" t="s">
         <v>76</v>
@@ -1978,7 +2004,7 @@
       <c r="D1" s="51"/>
       <c r="E1" s="52"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="53" t="s">
         <v>14</v>
@@ -1987,16 +2013,16 @@
       <c r="D2" s="53"/>
       <c r="E2" s="54"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="204" t="s">
+      <c r="B3" s="206" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="E3" s="205"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C3" s="206"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="207"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -2007,7 +2033,7 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>77</v>
       </c>
@@ -2020,7 +2046,7 @@
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>25</v>
       </c>
@@ -2031,57 +2057,57 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="207" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="209" t="s">
         <v>130</v>
       </c>
-      <c r="C8" s="207"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B9" s="207"/>
-      <c r="C9" s="207"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B10" s="207"/>
-      <c r="C10" s="207"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="206" t="s">
+      <c r="C8" s="209"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="209"/>
+      <c r="C9" s="209"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="209"/>
+      <c r="C10" s="209"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="208" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="206"/>
-      <c r="C13" s="206"/>
-      <c r="D13" s="206"/>
-      <c r="E13" s="206"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="206"/>
-      <c r="B14" s="206"/>
-      <c r="C14" s="206"/>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="206"/>
-      <c r="B15" s="206"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="206"/>
-      <c r="E15" s="206"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="206"/>
-      <c r="B16" s="206"/>
-      <c r="C16" s="206"/>
-      <c r="D16" s="206"/>
-      <c r="E16" s="206"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="208"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="208"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="208"/>
+      <c r="B15" s="208"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="208"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>106</v>
       </c>
@@ -2090,7 +2116,7 @@
       <c r="D20" s="7"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>79</v>
       </c>
@@ -2099,11 +2125,11 @@
       <c r="D21" s="116"/>
       <c r="E21" s="102"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="197" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="204" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="198"/>
+      <c r="B22" s="205"/>
       <c r="C22" s="39"/>
       <c r="D22" s="117">
         <v>473045</v>
@@ -2113,15 +2139,15 @@
       </c>
       <c r="H22" s="91"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="197"/>
-      <c r="B23" s="198"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="204"/>
+      <c r="B23" s="205"/>
       <c r="C23" s="39"/>
       <c r="D23" s="117"/>
       <c r="E23" s="110"/>
       <c r="H23" s="91"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
@@ -2133,7 +2159,7 @@
         <v>473045</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>17</v>
       </c>
@@ -2142,20 +2168,20 @@
       <c r="D25" s="119"/>
       <c r="E25" s="130"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="197" t="s">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="204" t="s">
         <v>125</v>
       </c>
-      <c r="B26" s="198"/>
+      <c r="B26" s="205"/>
       <c r="C26" s="41"/>
       <c r="D26" s="181">
         <v>74584</v>
       </c>
-      <c r="E26" s="243" t="s">
+      <c r="E26" s="201" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
         <v>1</v>
       </c>
@@ -2167,7 +2193,7 @@
         <v>74584</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>10</v>
       </c>
@@ -2176,7 +2202,7 @@
       <c r="D28" s="120"/>
       <c r="E28" s="106"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>69</v>
       </c>
@@ -2185,9 +2211,11 @@
       <c r="D29" s="111">
         <v>275382.28999999998</v>
       </c>
-      <c r="E29" s="110"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E29" s="110" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>68</v>
       </c>
@@ -2200,20 +2228,18 @@
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B31" s="127"/>
       <c r="C31" s="5"/>
       <c r="D31" s="111">
-        <v>275382.28999999998</v>
-      </c>
-      <c r="E31" s="110" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="E31" s="110"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="202" t="s">
         <v>70</v>
       </c>
@@ -2226,7 +2252,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="113" t="s">
         <v>80</v>
       </c>
@@ -2239,7 +2265,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
         <v>2</v>
       </c>
@@ -2248,21 +2274,21 @@
       <c r="D34" s="121"/>
       <c r="E34" s="104">
         <f>SUM(D29:D33)</f>
-        <v>753110.28999999992</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>477728</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="25"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="118"/>
       <c r="E35" s="107"/>
     </row>
-    <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="197" t="s">
+    <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="204" t="s">
         <v>119</v>
       </c>
-      <c r="B36" s="198"/>
+      <c r="B36" s="205"/>
       <c r="C36" s="5"/>
       <c r="D36" s="111">
         <v>75000</v>
@@ -2271,7 +2297,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="128" t="s">
         <v>138</v>
       </c>
@@ -2284,8 +2310,8 @@
         <v>139</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="239" t="s">
+    <row r="38" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="197" t="s">
         <v>143</v>
       </c>
       <c r="B38" s="129"/>
@@ -2297,7 +2323,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="128" t="s">
         <v>142</v>
       </c>
@@ -2310,8 +2336,8 @@
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="239" t="s">
+    <row r="40" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="197" t="s">
         <v>140</v>
       </c>
       <c r="B40" s="129"/>
@@ -2322,13 +2348,13 @@
       <c r="E40" s="112" t="s">
         <v>141</v>
       </c>
-      <c r="F40" s="240"/>
-    </row>
-    <row r="41" spans="1:7" ht="37" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="197" t="s">
+      <c r="F40" s="198"/>
+    </row>
+    <row r="41" spans="1:7" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="204" t="s">
         <v>148</v>
       </c>
-      <c r="B41" s="198"/>
+      <c r="B41" s="205"/>
       <c r="C41" s="5"/>
       <c r="D41" s="76">
         <v>56875.79</v>
@@ -2336,14 +2362,14 @@
       <c r="E41" s="112" t="s">
         <v>144</v>
       </c>
-      <c r="F41" s="240"/>
-      <c r="G41" s="240"/>
-    </row>
-    <row r="42" spans="1:7" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="197" t="s">
+      <c r="F41" s="198"/>
+      <c r="G41" s="198"/>
+    </row>
+    <row r="42" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="204" t="s">
         <v>145</v>
       </c>
-      <c r="B42" s="198"/>
+      <c r="B42" s="205"/>
       <c r="C42" s="5"/>
       <c r="D42" s="76">
         <v>320000</v>
@@ -2351,10 +2377,10 @@
       <c r="E42" s="112" t="s">
         <v>146</v>
       </c>
-      <c r="F42" s="240"/>
-      <c r="G42" s="240"/>
-    </row>
-    <row r="43" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F42" s="198"/>
+      <c r="G42" s="198"/>
+    </row>
+    <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="128" t="s">
         <v>124</v>
       </c>
@@ -2367,7 +2393,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>6</v>
       </c>
@@ -2379,7 +2405,7 @@
         <v>614648.12</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25" t="s">
         <v>11</v>
       </c>
@@ -2388,11 +2414,11 @@
       <c r="D45" s="116"/>
       <c r="E45" s="102"/>
     </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="197" t="s">
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="204" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="198"/>
+      <c r="B46" s="205"/>
       <c r="C46" s="39"/>
       <c r="D46" s="117">
         <v>150000</v>
@@ -2404,14 +2430,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="128"/>
       <c r="B47" s="129"/>
       <c r="C47" s="39"/>
       <c r="D47" s="144"/>
       <c r="E47" s="134"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
         <v>9</v>
       </c>
@@ -2423,7 +2449,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
         <v>8</v>
       </c>
@@ -2432,7 +2458,7 @@
       <c r="D49" s="115"/>
       <c r="E49" s="103"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>27</v>
       </c>
@@ -2441,7 +2467,7 @@
       <c r="D50" s="111"/>
       <c r="E50" s="108"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>118</v>
       </c>
@@ -2452,7 +2478,7 @@
       </c>
       <c r="E51" s="29"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="38" t="s">
         <v>9</v>
       </c>
@@ -2464,14 +2490,14 @@
         <v>21963.1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="73"/>
       <c r="E53" s="79"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="22" t="s">
         <v>102</v>
       </c>
@@ -2479,17 +2505,17 @@
       <c r="C54" s="22"/>
       <c r="D54" s="80"/>
       <c r="E54" s="133">
-        <f>2200000-2087350.51</f>
-        <v>112649.48999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <f>2200000-1811968.22</f>
+        <v>388031.78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="D55" s="81"/>
       <c r="E55" s="82"/>
       <c r="F55" s="31"/>
     </row>
-    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>98</v>
       </c>
@@ -2503,16 +2529,16 @@
       <c r="F56" s="101"/>
       <c r="G56" s="31"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D57" s="81"/>
       <c r="E57" s="81"/>
     </row>
-    <row r="58" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D58" s="81"/>
       <c r="E58" s="81"/>
       <c r="H58" s="122"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
         <v>99</v>
       </c>
@@ -2521,35 +2547,35 @@
       <c r="D59" s="85"/>
       <c r="E59" s="86"/>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="75"/>
       <c r="B60" s="109"/>
       <c r="C60" s="5"/>
       <c r="D60" s="76"/>
       <c r="E60" s="74"/>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="201"/>
-      <c r="B61" s="201"/>
+    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="212"/>
+      <c r="B61" s="212"/>
       <c r="C61" s="5"/>
       <c r="D61" s="111"/>
       <c r="E61" s="74"/>
     </row>
-    <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="75"/>
       <c r="B63" s="77"/>
       <c r="C63" s="5"/>
       <c r="D63" s="76"/>
       <c r="E63" s="74"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="36"/>
       <c r="B64" s="35"/>
       <c r="C64" s="35"/>
@@ -2559,9 +2585,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="22" t="s">
         <v>101</v>
       </c>
@@ -2570,8 +2596,8 @@
       <c r="D67" s="23"/>
       <c r="E67" s="196"/>
     </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>100</v>
       </c>
@@ -2583,8 +2609,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="71" t="s">
         <v>107</v>
       </c>
@@ -2593,16 +2619,16 @@
         <v>2200000</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="71" t="s">
         <v>108</v>
       </c>
       <c r="B72" s="72">
         <f>E56-E54</f>
-        <v>2087350.51</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>1811968.22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="71" t="s">
         <v>109</v>
       </c>
@@ -2611,7 +2637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="71" t="s">
         <v>110</v>
       </c>
@@ -2620,12 +2646,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="B76" s="30"/>
       <c r="C76" s="27"/>
     </row>
-    <row r="77" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="93" t="s">
         <v>111</v>
       </c>
@@ -2635,16 +2661,16 @@
       <c r="C77" s="27"/>
       <c r="D77" s="34"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="41" t="s">
         <v>104</v>
       </c>
       <c r="B78" s="98">
         <f>-B72</f>
-        <v>-2087350.51</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+        <v>-1811968.22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="41" t="s">
         <v>26</v>
       </c>
@@ -2653,7 +2679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="41" t="s">
         <v>113</v>
       </c>
@@ -2662,34 +2688,34 @@
         <v>2003377.2999999993</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="41" t="s">
         <v>126</v>
       </c>
       <c r="B81" s="99"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="100" t="s">
         <v>24</v>
       </c>
       <c r="B82" s="123"/>
     </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="96" t="s">
         <v>115</v>
       </c>
       <c r="B83" s="97">
         <f>SUM(B77:C82)</f>
-        <v>-756499.31000000099</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+        <v>-481117.02000000095</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="94"/>
       <c r="B84" s="94"/>
       <c r="D84" s="31"/>
       <c r="E84" s="30"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="93" t="s">
         <v>112</v>
       </c>
@@ -2699,7 +2725,7 @@
       <c r="D85" s="30"/>
       <c r="E85" s="31"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="41" t="s">
         <v>105</v>
       </c>
@@ -2709,7 +2735,7 @@
       </c>
       <c r="D86" s="31"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="41" t="s">
         <v>26</v>
       </c>
@@ -2719,22 +2745,22 @@
       </c>
       <c r="D87" s="31"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="41" t="s">
         <v>114</v>
       </c>
       <c r="B88" s="99">
         <v>0</v>
       </c>
-      <c r="D88" s="240"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D88" s="198"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="100" t="s">
         <v>24</v>
       </c>
       <c r="B89" s="123"/>
     </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="96" t="s">
         <v>116</v>
       </c>
@@ -2743,28 +2769,28 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="94"/>
       <c r="B91" s="94"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="94"/>
       <c r="B92" s="94"/>
     </row>
-    <row r="93" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" s="200" t="s">
+    <row r="93" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="211" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="200"/>
-      <c r="C94" s="200"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A95" s="200"/>
-      <c r="B95" s="200"/>
-      <c r="C95" s="200"/>
-    </row>
-    <row r="96" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B94" s="211"/>
+      <c r="C94" s="211"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="211"/>
+      <c r="B95" s="211"/>
+      <c r="C95" s="211"/>
+    </row>
+    <row r="96" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="88"/>
       <c r="B96" s="26"/>
       <c r="C96" s="26">
@@ -2772,13 +2798,13 @@
       </c>
       <c r="E96" s="101"/>
     </row>
-    <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="88"/>
       <c r="B97" s="90"/>
       <c r="C97" s="87"/>
       <c r="D97" s="101"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="32" t="s">
         <v>6</v>
       </c>
@@ -2788,39 +2814,46 @@
       </c>
       <c r="C98" s="33"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M99" s="6"/>
     </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="199"/>
-      <c r="B100" s="199"/>
-      <c r="C100" s="199"/>
-      <c r="D100" s="199"/>
-      <c r="E100" s="199"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A101" s="199"/>
-      <c r="B101" s="199"/>
-      <c r="C101" s="199"/>
-      <c r="D101" s="199"/>
-      <c r="E101" s="199"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A102" s="199"/>
-      <c r="B102" s="199"/>
-      <c r="C102" s="199"/>
-      <c r="D102" s="199"/>
-      <c r="E102" s="199"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A103" s="199"/>
-      <c r="B103" s="199"/>
-      <c r="C103" s="199"/>
-      <c r="D103" s="199"/>
-      <c r="E103" s="199"/>
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="210"/>
+      <c r="B100" s="210"/>
+      <c r="C100" s="210"/>
+      <c r="D100" s="210"/>
+      <c r="E100" s="210"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="210"/>
+      <c r="B101" s="210"/>
+      <c r="C101" s="210"/>
+      <c r="D101" s="210"/>
+      <c r="E101" s="210"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="210"/>
+      <c r="B102" s="210"/>
+      <c r="C102" s="210"/>
+      <c r="D102" s="210"/>
+      <c r="E102" s="210"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="210"/>
+      <c r="B103" s="210"/>
+      <c r="C103" s="210"/>
+      <c r="D103" s="210"/>
+      <c r="E103" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A100:E103"/>
+    <mergeCell ref="A94:C95"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2828,13 +2861,6 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A100:E103"/>
-    <mergeCell ref="A94:C95"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A41:B41"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2845,47 +2871,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.36328125" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.453125" customWidth="1"/>
-    <col min="6" max="6" width="14.08984375" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
-    <col min="8" max="8" width="10.54296875" customWidth="1"/>
-    <col min="9" max="9" width="9.54296875" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" customWidth="1"/>
-    <col min="11" max="11" width="12.453125" customWidth="1"/>
-    <col min="12" max="12" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" customWidth="1"/>
-    <col min="14" max="14" width="14.6328125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.36328125" customWidth="1"/>
-    <col min="17" max="17" width="7.36328125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="148"/>
       <c r="B1" s="149"/>
       <c r="C1" s="150"/>
       <c r="D1" s="150"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="211"/>
-      <c r="M1" s="211"/>
-      <c r="N1" s="211"/>
+      <c r="E1" s="213"/>
+      <c r="F1" s="213"/>
+      <c r="G1" s="213"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="213"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="213"/>
+      <c r="M1" s="213"/>
+      <c r="N1" s="213"/>
       <c r="O1" s="149"/>
       <c r="P1" s="151"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="152"/>
       <c r="B2" s="153"/>
       <c r="C2" s="154"/>
@@ -2912,7 +2936,7 @@
       <c r="P2" s="161"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="152"/>
       <c r="B3" s="153"/>
       <c r="C3" s="154"/>
@@ -2931,212 +2955,212 @@
       <c r="P3" s="161"/>
       <c r="Q3" s="20"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="221" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="225" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="222"/>
-      <c r="C4" s="222"/>
-      <c r="D4" s="222"/>
-      <c r="E4" s="222"/>
-      <c r="F4" s="222"/>
-      <c r="G4" s="222"/>
-      <c r="H4" s="222"/>
-      <c r="I4" s="222"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="222"/>
-      <c r="L4" s="222"/>
-      <c r="M4" s="222"/>
-      <c r="N4" s="222"/>
-      <c r="O4" s="222"/>
-      <c r="P4" s="223"/>
+      <c r="B4" s="226"/>
+      <c r="C4" s="226"/>
+      <c r="D4" s="226"/>
+      <c r="E4" s="226"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="226"/>
+      <c r="H4" s="226"/>
+      <c r="I4" s="226"/>
+      <c r="J4" s="226"/>
+      <c r="K4" s="226"/>
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="226"/>
+      <c r="O4" s="226"/>
+      <c r="P4" s="227"/>
       <c r="Q4" s="20"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A5" s="224"/>
-      <c r="B5" s="225"/>
-      <c r="C5" s="225"/>
-      <c r="D5" s="225"/>
-      <c r="E5" s="225"/>
-      <c r="F5" s="225"/>
-      <c r="G5" s="225"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="225"/>
-      <c r="K5" s="225"/>
-      <c r="L5" s="225"/>
-      <c r="M5" s="225"/>
-      <c r="N5" s="225"/>
-      <c r="O5" s="225"/>
-      <c r="P5" s="226"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="228"/>
+      <c r="B5" s="229"/>
+      <c r="C5" s="229"/>
+      <c r="D5" s="229"/>
+      <c r="E5" s="229"/>
+      <c r="F5" s="229"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="229"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="229"/>
+      <c r="L5" s="229"/>
+      <c r="M5" s="229"/>
+      <c r="N5" s="229"/>
+      <c r="O5" s="229"/>
+      <c r="P5" s="230"/>
       <c r="Q5" s="20"/>
     </row>
-    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="224"/>
-      <c r="B6" s="225"/>
-      <c r="C6" s="225"/>
-      <c r="D6" s="225"/>
-      <c r="E6" s="225"/>
-      <c r="F6" s="225"/>
-      <c r="G6" s="225"/>
-      <c r="H6" s="225"/>
-      <c r="I6" s="225"/>
-      <c r="J6" s="225"/>
-      <c r="K6" s="225"/>
-      <c r="L6" s="225"/>
-      <c r="M6" s="225"/>
-      <c r="N6" s="225"/>
-      <c r="O6" s="225"/>
-      <c r="P6" s="226"/>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="228"/>
+      <c r="B6" s="229"/>
+      <c r="C6" s="229"/>
+      <c r="D6" s="229"/>
+      <c r="E6" s="229"/>
+      <c r="F6" s="229"/>
+      <c r="G6" s="229"/>
+      <c r="H6" s="229"/>
+      <c r="I6" s="229"/>
+      <c r="J6" s="229"/>
+      <c r="K6" s="229"/>
+      <c r="L6" s="229"/>
+      <c r="M6" s="229"/>
+      <c r="N6" s="229"/>
+      <c r="O6" s="229"/>
+      <c r="P6" s="230"/>
       <c r="Q6" s="20"/>
     </row>
-    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="224"/>
-      <c r="B7" s="225"/>
-      <c r="C7" s="225"/>
-      <c r="D7" s="225"/>
-      <c r="E7" s="225"/>
-      <c r="F7" s="225"/>
-      <c r="G7" s="225"/>
-      <c r="H7" s="225"/>
-      <c r="I7" s="225"/>
-      <c r="J7" s="225"/>
-      <c r="K7" s="225"/>
-      <c r="L7" s="225"/>
-      <c r="M7" s="225"/>
-      <c r="N7" s="225"/>
-      <c r="O7" s="225"/>
-      <c r="P7" s="226"/>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="228"/>
+      <c r="B7" s="229"/>
+      <c r="C7" s="229"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="229"/>
+      <c r="F7" s="229"/>
+      <c r="G7" s="229"/>
+      <c r="H7" s="229"/>
+      <c r="I7" s="229"/>
+      <c r="J7" s="229"/>
+      <c r="K7" s="229"/>
+      <c r="L7" s="229"/>
+      <c r="M7" s="229"/>
+      <c r="N7" s="229"/>
+      <c r="O7" s="229"/>
+      <c r="P7" s="230"/>
       <c r="Q7" s="20"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="227"/>
-      <c r="B8" s="228"/>
-      <c r="C8" s="228"/>
-      <c r="D8" s="228"/>
-      <c r="E8" s="228"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="228"/>
-      <c r="H8" s="228"/>
-      <c r="I8" s="228"/>
-      <c r="J8" s="228"/>
-      <c r="K8" s="228"/>
-      <c r="L8" s="228"/>
-      <c r="M8" s="228"/>
-      <c r="N8" s="228"/>
-      <c r="O8" s="228"/>
-      <c r="P8" s="229"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="232" t="s">
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="231"/>
+      <c r="B8" s="232"/>
+      <c r="C8" s="232"/>
+      <c r="D8" s="232"/>
+      <c r="E8" s="232"/>
+      <c r="F8" s="232"/>
+      <c r="G8" s="232"/>
+      <c r="H8" s="232"/>
+      <c r="I8" s="232"/>
+      <c r="J8" s="232"/>
+      <c r="K8" s="232"/>
+      <c r="L8" s="232"/>
+      <c r="M8" s="232"/>
+      <c r="N8" s="232"/>
+      <c r="O8" s="232"/>
+      <c r="P8" s="233"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="236" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="233"/>
-      <c r="C9" s="233"/>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
-      <c r="M9" s="233"/>
-      <c r="N9" s="233"/>
-      <c r="O9" s="233"/>
-      <c r="P9" s="233"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="234" t="s">
+      <c r="B9" s="237"/>
+      <c r="C9" s="237"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="237"/>
+      <c r="F9" s="237"/>
+      <c r="G9" s="237"/>
+      <c r="H9" s="237"/>
+      <c r="I9" s="237"/>
+      <c r="J9" s="237"/>
+      <c r="K9" s="237"/>
+      <c r="L9" s="237"/>
+      <c r="M9" s="237"/>
+      <c r="N9" s="237"/>
+      <c r="O9" s="237"/>
+      <c r="P9" s="237"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="238" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="234"/>
-      <c r="C10" s="234"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="234"/>
-      <c r="F10" s="234"/>
-      <c r="G10" s="234"/>
-      <c r="H10" s="234"/>
-      <c r="I10" s="234"/>
-      <c r="J10" s="234"/>
-      <c r="K10" s="234"/>
-      <c r="L10" s="234"/>
-      <c r="M10" s="234"/>
-      <c r="N10" s="234"/>
-      <c r="O10" s="234"/>
-      <c r="P10" s="234"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A11" s="208" t="s">
+      <c r="B10" s="238"/>
+      <c r="C10" s="238"/>
+      <c r="D10" s="238"/>
+      <c r="E10" s="238"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="238"/>
+      <c r="H10" s="238"/>
+      <c r="I10" s="238"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="238"/>
+      <c r="L10" s="238"/>
+      <c r="M10" s="238"/>
+      <c r="N10" s="238"/>
+      <c r="O10" s="238"/>
+      <c r="P10" s="238"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="218" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="124"/>
-      <c r="C11" s="208" t="s">
+      <c r="C11" s="218" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="208" t="s">
+      <c r="D11" s="218" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="208" t="s">
+      <c r="E11" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="212" t="s">
+      <c r="F11" s="214" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="208" t="s">
+      <c r="G11" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="216" t="s">
+      <c r="H11" s="220" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="212" t="s">
+      <c r="I11" s="214" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="212" t="s">
+      <c r="J11" s="214" t="s">
         <v>81</v>
       </c>
-      <c r="K11" s="212" t="s">
+      <c r="K11" s="214" t="s">
         <v>96</v>
       </c>
-      <c r="L11" s="219" t="s">
+      <c r="L11" s="223" t="s">
         <v>97</v>
       </c>
-      <c r="M11" s="212" t="s">
+      <c r="M11" s="214" t="s">
         <v>81</v>
       </c>
       <c r="N11" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="214" t="s">
+      <c r="O11" s="216" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="230" t="s">
+      <c r="P11" s="234" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="210"/>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="219"/>
       <c r="B12" s="125"/>
-      <c r="C12" s="210"/>
-      <c r="D12" s="209"/>
-      <c r="E12" s="210"/>
-      <c r="F12" s="213"/>
-      <c r="G12" s="210"/>
-      <c r="H12" s="217"/>
-      <c r="I12" s="213"/>
-      <c r="J12" s="218"/>
-      <c r="K12" s="213"/>
-      <c r="L12" s="220"/>
-      <c r="M12" s="213"/>
+      <c r="C12" s="219"/>
+      <c r="D12" s="239"/>
+      <c r="E12" s="219"/>
+      <c r="F12" s="215"/>
+      <c r="G12" s="219"/>
+      <c r="H12" s="221"/>
+      <c r="I12" s="215"/>
+      <c r="J12" s="222"/>
+      <c r="K12" s="215"/>
+      <c r="L12" s="224"/>
+      <c r="M12" s="215"/>
       <c r="N12" s="43" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="O12" s="215"/>
-      <c r="P12" s="231"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O12" s="217"/>
+      <c r="P12" s="235"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="46">
         <v>1</v>
       </c>
@@ -3197,7 +3221,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="46">
         <v>2</v>
       </c>
@@ -3258,7 +3282,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="46">
         <v>3</v>
       </c>
@@ -3322,7 +3346,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="46">
         <v>4</v>
       </c>
@@ -3386,7 +3410,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="164">
         <v>5</v>
       </c>
@@ -3406,7 +3430,7 @@
         <v>132000.04999999999</v>
       </c>
       <c r="G17" s="166">
-        <f t="shared" ref="G17:G21" si="8">F17</f>
+        <f t="shared" ref="G17:G18" si="8">F17</f>
         <v>132000.04999999999</v>
       </c>
       <c r="H17" s="167">
@@ -3453,7 +3477,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="46">
         <v>6</v>
       </c>
@@ -3517,7 +3541,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="183">
         <v>7</v>
       </c>
@@ -3578,7 +3602,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="183">
         <v>8</v>
       </c>
@@ -3642,7 +3666,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="46">
         <v>9</v>
       </c>
@@ -3706,7 +3730,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="46">
         <v>10</v>
       </c>
@@ -3770,7 +3794,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="46">
         <v>11</v>
       </c>
@@ -3835,7 +3859,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="46">
         <v>12</v>
       </c>
@@ -3899,7 +3923,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="46">
         <v>13</v>
       </c>
@@ -3962,7 +3986,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="164">
         <v>14</v>
       </c>
@@ -4023,7 +4047,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="46">
         <v>15</v>
       </c>
@@ -4041,7 +4065,7 @@
         <v>108000.15</v>
       </c>
       <c r="G27" s="57">
-        <f>F27</f>
+        <f t="shared" ref="G27:G35" si="9">F27</f>
         <v>108000.15</v>
       </c>
       <c r="H27" s="58">
@@ -4085,7 +4109,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="46">
         <v>16</v>
       </c>
@@ -4105,7 +4129,7 @@
         <v>14000.16</v>
       </c>
       <c r="G28" s="57">
-        <f>F28</f>
+        <f t="shared" si="9"/>
         <v>14000.16</v>
       </c>
       <c r="H28" s="58">
@@ -4149,7 +4173,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="46">
         <v>17</v>
       </c>
@@ -4167,7 +4191,7 @@
         <v>12000.17</v>
       </c>
       <c r="G29" s="57">
-        <f>F29</f>
+        <f t="shared" si="9"/>
         <v>12000.17</v>
       </c>
       <c r="H29" s="58">
@@ -4211,7 +4235,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="46">
         <v>18</v>
       </c>
@@ -4229,7 +4253,7 @@
         <v>12000.18</v>
       </c>
       <c r="G30" s="57">
-        <f>F30</f>
+        <f t="shared" si="9"/>
         <v>12000.18</v>
       </c>
       <c r="H30" s="58">
@@ -4273,7 +4297,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="183">
         <v>19</v>
       </c>
@@ -4291,7 +4315,7 @@
         <v>11640.19</v>
       </c>
       <c r="G31" s="57">
-        <f>F31</f>
+        <f t="shared" si="9"/>
         <v>11640.19</v>
       </c>
       <c r="H31" s="186">
@@ -4314,11 +4338,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M31" s="241">
+      <c r="M31" s="199">
         <f>EDESUR!I25</f>
         <v>0</v>
       </c>
-      <c r="N31" s="242">
+      <c r="N31" s="200">
         <f t="shared" si="4"/>
         <v>13200.19</v>
       </c>
@@ -4332,7 +4356,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A32" s="62">
         <v>20</v>
       </c>
@@ -4352,7 +4376,7 @@
         <v>12000.2</v>
       </c>
       <c r="G32" s="57">
-        <f>F32</f>
+        <f t="shared" si="9"/>
         <v>12000.2</v>
       </c>
       <c r="H32" s="58">
@@ -4389,11 +4413,11 @@
         <v>13596.2</v>
       </c>
       <c r="Q32" s="31">
-        <f t="shared" ref="Q32:Q35" si="9">Q31+0.01</f>
+        <f t="shared" ref="Q32:Q35" si="10">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="62">
         <v>21</v>
       </c>
@@ -4413,7 +4437,7 @@
         <v>6000.21</v>
       </c>
       <c r="G33" s="57">
-        <f>F33</f>
+        <f t="shared" si="9"/>
         <v>6000.21</v>
       </c>
       <c r="H33" s="58">
@@ -4450,11 +4474,11 @@
         <v>6798.21</v>
       </c>
       <c r="Q33" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="63">
         <v>22</v>
       </c>
@@ -4472,7 +4496,7 @@
         <v>6000.22</v>
       </c>
       <c r="G34" s="180">
-        <f>F34</f>
+        <f t="shared" si="9"/>
         <v>6000.22</v>
       </c>
       <c r="H34" s="58">
@@ -4509,11 +4533,11 @@
         <v>6798.22</v>
       </c>
       <c r="Q34" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="46">
         <v>23</v>
       </c>
@@ -4533,7 +4557,7 @@
         <v>6000.23</v>
       </c>
       <c r="G35" s="57">
-        <f>F35</f>
+        <f t="shared" si="9"/>
         <v>6000.23</v>
       </c>
       <c r="H35" s="58">
@@ -4570,11 +4594,11 @@
         <v>6798.23</v>
       </c>
       <c r="Q35" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="67"/>
       <c r="B36" s="67"/>
       <c r="C36" s="68"/>
@@ -4596,19 +4620,19 @@
         <v>125953.46000000004</v>
       </c>
       <c r="I36" s="44">
-        <f t="shared" ref="I36:O36" si="10">SUM(I13:I35)</f>
+        <f t="shared" ref="I36:O36" si="11">SUM(I13:I35)</f>
         <v>7537.2168000000001</v>
       </c>
       <c r="J36" s="44">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>177260.87950743397</v>
       </c>
       <c r="K36" s="95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2200000</v>
       </c>
       <c r="L36" s="44">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M36" s="191"/>
@@ -4617,7 +4641,7 @@
         <v>2599383.7600000012</v>
       </c>
       <c r="O36" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2706373.7100000009</v>
       </c>
       <c r="P36" s="69">
@@ -4625,100 +4649,105 @@
         <v>2677365.7600000012</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C39" s="199" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="210" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="199"/>
-      <c r="E39" s="199"/>
-      <c r="F39" s="199"/>
-      <c r="G39" s="199"/>
-      <c r="H39" s="199"/>
-      <c r="I39" s="199"/>
-      <c r="J39" s="199"/>
-      <c r="K39" s="199"/>
-      <c r="L39" s="199"/>
-      <c r="M39" s="199"/>
-      <c r="N39" s="199"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="199"/>
-      <c r="D40" s="199"/>
-      <c r="E40" s="199"/>
-      <c r="F40" s="199"/>
-      <c r="G40" s="199"/>
-      <c r="H40" s="199"/>
-      <c r="I40" s="199"/>
-      <c r="J40" s="199"/>
-      <c r="K40" s="199"/>
-      <c r="L40" s="199"/>
-      <c r="M40" s="199"/>
-      <c r="N40" s="199"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="199"/>
-      <c r="D41" s="199"/>
-      <c r="E41" s="199"/>
-      <c r="F41" s="199"/>
-      <c r="G41" s="199"/>
-      <c r="H41" s="199"/>
-      <c r="I41" s="199"/>
-      <c r="J41" s="199"/>
-      <c r="K41" s="199"/>
-      <c r="L41" s="199"/>
-      <c r="M41" s="199"/>
-      <c r="N41" s="199"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C42" s="199"/>
-      <c r="D42" s="199"/>
-      <c r="E42" s="199"/>
-      <c r="F42" s="199"/>
-      <c r="G42" s="199"/>
-      <c r="H42" s="199"/>
-      <c r="I42" s="199"/>
-      <c r="J42" s="199"/>
-      <c r="K42" s="199"/>
-      <c r="L42" s="199"/>
-      <c r="M42" s="199"/>
-      <c r="N42" s="199"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C43" s="199"/>
-      <c r="D43" s="199"/>
-      <c r="E43" s="199"/>
-      <c r="F43" s="199"/>
-      <c r="G43" s="199"/>
-      <c r="H43" s="199"/>
-      <c r="I43" s="199"/>
-      <c r="J43" s="199"/>
-      <c r="K43" s="199"/>
-      <c r="L43" s="199"/>
-      <c r="M43" s="199"/>
-      <c r="N43" s="199"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C44" s="199"/>
-      <c r="D44" s="199"/>
-      <c r="E44" s="199"/>
-      <c r="F44" s="199"/>
-      <c r="G44" s="199"/>
-      <c r="H44" s="199"/>
-      <c r="I44" s="199"/>
-      <c r="J44" s="199"/>
-      <c r="K44" s="199"/>
-      <c r="L44" s="199"/>
-      <c r="M44" s="199"/>
-      <c r="N44" s="199"/>
+      <c r="D39" s="210"/>
+      <c r="E39" s="210"/>
+      <c r="F39" s="210"/>
+      <c r="G39" s="210"/>
+      <c r="H39" s="210"/>
+      <c r="I39" s="210"/>
+      <c r="J39" s="210"/>
+      <c r="K39" s="210"/>
+      <c r="L39" s="210"/>
+      <c r="M39" s="210"/>
+      <c r="N39" s="210"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="210"/>
+      <c r="D40" s="210"/>
+      <c r="E40" s="210"/>
+      <c r="F40" s="210"/>
+      <c r="G40" s="210"/>
+      <c r="H40" s="210"/>
+      <c r="I40" s="210"/>
+      <c r="J40" s="210"/>
+      <c r="K40" s="210"/>
+      <c r="L40" s="210"/>
+      <c r="M40" s="210"/>
+      <c r="N40" s="210"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="210"/>
+      <c r="D41" s="210"/>
+      <c r="E41" s="210"/>
+      <c r="F41" s="210"/>
+      <c r="G41" s="210"/>
+      <c r="H41" s="210"/>
+      <c r="I41" s="210"/>
+      <c r="J41" s="210"/>
+      <c r="K41" s="210"/>
+      <c r="L41" s="210"/>
+      <c r="M41" s="210"/>
+      <c r="N41" s="210"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="210"/>
+      <c r="D42" s="210"/>
+      <c r="E42" s="210"/>
+      <c r="F42" s="210"/>
+      <c r="G42" s="210"/>
+      <c r="H42" s="210"/>
+      <c r="I42" s="210"/>
+      <c r="J42" s="210"/>
+      <c r="K42" s="210"/>
+      <c r="L42" s="210"/>
+      <c r="M42" s="210"/>
+      <c r="N42" s="210"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="210"/>
+      <c r="D43" s="210"/>
+      <c r="E43" s="210"/>
+      <c r="F43" s="210"/>
+      <c r="G43" s="210"/>
+      <c r="H43" s="210"/>
+      <c r="I43" s="210"/>
+      <c r="J43" s="210"/>
+      <c r="K43" s="210"/>
+      <c r="L43" s="210"/>
+      <c r="M43" s="210"/>
+      <c r="N43" s="210"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="210"/>
+      <c r="D44" s="210"/>
+      <c r="E44" s="210"/>
+      <c r="F44" s="210"/>
+      <c r="G44" s="210"/>
+      <c r="H44" s="210"/>
+      <c r="I44" s="210"/>
+      <c r="J44" s="210"/>
+      <c r="K44" s="210"/>
+      <c r="L44" s="210"/>
+      <c r="M44" s="210"/>
+      <c r="N44" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4733,11 +4762,6 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="M11:M12"/>
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4747,17 +4771,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.6328125" customWidth="1"/>
-    <col min="6" max="6" width="4.54296875" customWidth="1"/>
-    <col min="7" max="7" width="24.453125" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.54296875" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="135" t="s">
         <v>82</v>
       </c>
@@ -4770,20 +4794,20 @@
       <c r="G3" s="179" t="s">
         <v>123</v>
       </c>
-      <c r="I3" s="235" t="s">
+      <c r="I3" s="242" t="s">
         <v>90</v>
       </c>
-      <c r="J3" s="236"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J3" s="243"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="135"/>
       <c r="C4" s="135"/>
       <c r="E4" s="135"/>
       <c r="G4" s="138"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="236"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I4" s="242"/>
+      <c r="J4" s="243"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="135">
         <v>1</v>
       </c>
@@ -4797,13 +4821,13 @@
       <c r="G5" s="140">
         <v>4843.2564768292677</v>
       </c>
-      <c r="I5" s="237">
+      <c r="I5" s="240">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="238"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J5" s="241"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="135">
         <v>1</v>
       </c>
@@ -4817,13 +4841,13 @@
       <c r="G6" s="140">
         <v>0</v>
       </c>
-      <c r="I6" s="237">
+      <c r="I6" s="240">
         <f t="shared" ref="I6:I21" si="0">E6-G6</f>
         <v>24102.857781768264</v>
       </c>
-      <c r="J6" s="238"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J6" s="241"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="135">
         <v>1</v>
       </c>
@@ -4837,13 +4861,13 @@
       <c r="G7" s="140">
         <v>10187.377552707869</v>
       </c>
-      <c r="I7" s="237">
+      <c r="I7" s="240">
         <f t="shared" si="0"/>
         <v>20750.545398450711</v>
       </c>
-      <c r="J7" s="238"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J7" s="241"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="135">
         <v>2</v>
       </c>
@@ -4857,13 +4881,13 @@
       <c r="G8" s="140">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I8" s="237">
+      <c r="I8" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="238"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J8" s="241"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="136">
         <v>2</v>
       </c>
@@ -4877,13 +4901,13 @@
       <c r="G9" s="140">
         <v>2663.7910622560971</v>
       </c>
-      <c r="I9" s="237">
+      <c r="I9" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="238"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J9" s="241"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="136">
         <v>2</v>
       </c>
@@ -4897,13 +4921,13 @@
       <c r="G10" s="140">
         <v>2663.7910622560971</v>
       </c>
-      <c r="I10" s="237">
+      <c r="I10" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="238"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J10" s="241"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="136">
         <v>2</v>
       </c>
@@ -4917,13 +4941,13 @@
       <c r="G11" s="140">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I11" s="237">
+      <c r="I11" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="238"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J11" s="241"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="136">
         <v>3</v>
       </c>
@@ -4937,13 +4961,13 @@
       <c r="G12" s="140">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I12" s="237">
+      <c r="I12" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="238"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J12" s="241"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="135">
         <v>3</v>
       </c>
@@ -4957,13 +4981,13 @@
       <c r="G13" s="140">
         <v>38595.439592416595</v>
       </c>
-      <c r="I13" s="237">
+      <c r="I13" s="240">
         <f t="shared" si="0"/>
         <v>43777.036573498022</v>
       </c>
-      <c r="J13" s="238"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J13" s="241"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="136">
         <v>3</v>
       </c>
@@ -4977,13 +5001,13 @@
       <c r="G14" s="140">
         <v>2663.7910622560971</v>
       </c>
-      <c r="I14" s="237">
+      <c r="I14" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="238"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J14" s="241"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="136">
         <v>3</v>
       </c>
@@ -4997,13 +5021,13 @@
       <c r="G15" s="140">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I15" s="237">
+      <c r="I15" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="238"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J15" s="241"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="135">
         <v>4</v>
       </c>
@@ -5017,13 +5041,13 @@
       <c r="G16" s="140">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I16" s="237">
+      <c r="I16" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="238"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J16" s="241"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="136">
         <v>4</v>
       </c>
@@ -5037,13 +5061,13 @@
       <c r="G17" s="140">
         <v>2663.7910622560971</v>
       </c>
-      <c r="I17" s="237">
+      <c r="I17" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="238"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J17" s="241"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="135">
         <v>4</v>
       </c>
@@ -5057,13 +5081,13 @@
       <c r="G18" s="140">
         <v>2663.7910622560971</v>
       </c>
-      <c r="I18" s="237">
+      <c r="I18" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="238"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J18" s="241"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="136">
         <v>4</v>
       </c>
@@ -5077,21 +5101,21 @@
       <c r="G19" s="140">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I19" s="237">
+      <c r="I19" s="240">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="238"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J19" s="241"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="135"/>
       <c r="C20" s="135"/>
       <c r="E20" s="135"/>
       <c r="G20" s="138"/>
-      <c r="I20" s="237"/>
-      <c r="J20" s="238"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I20" s="240"/>
+      <c r="J20" s="241"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="172" t="s">
         <v>122</v>
       </c>
@@ -5106,13 +5130,13 @@
         <f>SUM(G5:G20)</f>
         <v>80021.821420673266</v>
       </c>
-      <c r="I21" s="237">
+      <c r="I21" s="240">
         <f t="shared" si="0"/>
         <v>88630.439753716972</v>
       </c>
-      <c r="J21" s="238"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J21" s="241"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="135" t="s">
         <v>88</v>
       </c>
@@ -5126,13 +5150,13 @@
         <f>E22</f>
         <v>282.5232944817073</v>
       </c>
-      <c r="I22" s="237">
+      <c r="I22" s="240">
         <f t="shared" ref="I22" si="1">E22-G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="238"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J22" s="241"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="135" t="s">
         <v>88</v>
       </c>
@@ -5146,13 +5170,13 @@
         <f t="shared" ref="G23:G29" si="2">E23</f>
         <v>242.16282384146339</v>
       </c>
-      <c r="I23" s="237">
+      <c r="I23" s="240">
         <f t="shared" ref="I23:I31" si="3">E23-G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="238"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J23" s="241"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="135" t="s">
         <v>88</v>
       </c>
@@ -5166,13 +5190,13 @@
         <f t="shared" si="2"/>
         <v>242.16282384146339</v>
       </c>
-      <c r="I24" s="237">
+      <c r="I24" s="240">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="238"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J24" s="241"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="135" t="s">
         <v>88</v>
       </c>
@@ -5186,13 +5210,13 @@
         <f t="shared" si="2"/>
         <v>242.16282384146339</v>
       </c>
-      <c r="I25" s="237">
+      <c r="I25" s="240">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="238"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J25" s="241"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="135" t="s">
         <v>88</v>
       </c>
@@ -5206,13 +5230,13 @@
         <f t="shared" si="2"/>
         <v>242.16282384146339</v>
       </c>
-      <c r="I26" s="237">
+      <c r="I26" s="240">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="238"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J26" s="241"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="135" t="s">
         <v>88</v>
       </c>
@@ -5226,13 +5250,13 @@
         <f t="shared" si="2"/>
         <v>121.0814119207317</v>
       </c>
-      <c r="I27" s="237">
+      <c r="I27" s="240">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J27" s="238"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J27" s="241"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="135" t="s">
         <v>88</v>
       </c>
@@ -5246,13 +5270,13 @@
         <f t="shared" si="2"/>
         <v>121.0814119207317</v>
       </c>
-      <c r="I28" s="237">
+      <c r="I28" s="240">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J28" s="238"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J28" s="241"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="135" t="s">
         <v>88</v>
       </c>
@@ -5266,13 +5290,13 @@
         <f t="shared" si="2"/>
         <v>121.0814119207317</v>
       </c>
-      <c r="I29" s="237">
+      <c r="I29" s="240">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="238"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J29" s="241"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="177" t="s">
         <v>122</v>
       </c>
@@ -5287,28 +5311,28 @@
         <f>SUM(G22:G29)</f>
         <v>1614.4188256097557</v>
       </c>
-      <c r="I30" s="237">
+      <c r="I30" s="240">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="238"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J30" s="241"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E31" s="143"/>
       <c r="G31" s="140"/>
-      <c r="I31" s="237">
+      <c r="I31" s="240">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="238"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="J31" s="241"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E32" s="141"/>
       <c r="G32" s="142"/>
-      <c r="I32" s="237"/>
-      <c r="J32" s="238"/>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.35">
+      <c r="I32" s="240"/>
+      <c r="J32" s="241"/>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E33" s="143">
         <f>E30+E21</f>
         <v>170266.68</v>
@@ -5317,14 +5341,29 @@
         <f>G21+G30</f>
         <v>81636.240246283021</v>
       </c>
-      <c r="I33" s="237">
+      <c r="I33" s="240">
         <f>E33-G33</f>
         <v>88630.439753716972</v>
       </c>
-      <c r="J33" s="238"/>
+      <c r="J33" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5341,21 +5380,6 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>

--- a/2026/SALTA 1167/Febrero/SALTA1167-Febrero.xlsx
+++ b/2026/SALTA 1167/Febrero/SALTA1167-Febrero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAEAC11-6550-44F7-A905-B7F08ECCDB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FA8043-3133-4394-B44B-AD2EBF684BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -109,9 +109,6 @@
     <t xml:space="preserve">Punitorios mal cobrados </t>
   </si>
   <si>
-    <t>CONSORCIO DE PROPIETARIOS DEL EDIFICIO CALLE YRIGOYEN 9730</t>
-  </si>
-  <si>
     <t>Pagos sin identificar</t>
   </si>
   <si>
@@ -483,6 +480,9 @@
   </si>
   <si>
     <t>Easy Barracas - Compra de termotanque - Cuota 1  - Restan 6 cuotas de $157.988,29</t>
+  </si>
+  <si>
+    <t>CONSORCIO DE PROPIETARIOS DEL EDIFICIO CALLE SALTA 1167</t>
   </si>
 </sst>
 </file>
@@ -1998,7 +1998,7 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="B1" s="51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C1" s="51"/>
       <c r="D1" s="51"/>
@@ -2016,7 +2016,7 @@
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
       <c r="B3" s="206" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="206"/>
       <c r="D3" s="206"/>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="53" t="s">
@@ -2048,18 +2048,18 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="209" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="209"/>
     </row>
@@ -2074,7 +2074,7 @@
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="208" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="208"/>
       <c r="C13" s="208"/>
@@ -2109,7 +2109,7 @@
     <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="11"/>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -2127,7 +2127,7 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="204" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" s="205"/>
       <c r="C22" s="39"/>
@@ -2135,7 +2135,7 @@
         <v>473045</v>
       </c>
       <c r="E22" s="110" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H22" s="91"/>
     </row>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="204" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B26" s="205"/>
       <c r="C26" s="41"/>
@@ -2178,7 +2178,7 @@
         <v>74584</v>
       </c>
       <c r="E26" s="201" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -2204,20 +2204,16 @@
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="111">
-        <v>275382.28999999998</v>
-      </c>
-      <c r="E29" s="110" t="s">
-        <v>133</v>
-      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="110"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2225,23 +2221,25 @@
         <v>5432.38</v>
       </c>
       <c r="E30" s="110" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B31" s="127"/>
       <c r="C31" s="5"/>
       <c r="D31" s="111">
-        <v>0</v>
-      </c>
-      <c r="E31" s="110"/>
+        <v>275382.28999999998</v>
+      </c>
+      <c r="E31" s="110" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="202" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B32" s="203"/>
       <c r="C32" s="5"/>
@@ -2249,12 +2247,12 @@
         <v>174848.74</v>
       </c>
       <c r="E32" s="110" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="113" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B33" s="109"/>
       <c r="C33" s="5"/>
@@ -2262,7 +2260,7 @@
         <v>22064.59</v>
       </c>
       <c r="E33" s="110" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2286,7 +2284,7 @@
     </row>
     <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="204" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B36" s="205"/>
       <c r="C36" s="5"/>
@@ -2294,12 +2292,12 @@
         <v>75000</v>
       </c>
       <c r="E36" s="112" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="128" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B37" s="129"/>
       <c r="C37" s="5"/>
@@ -2307,12 +2305,12 @@
         <v>4800</v>
       </c>
       <c r="E37" s="112" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="197" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="129"/>
       <c r="C38" s="5"/>
@@ -2320,12 +2318,12 @@
         <v>24000</v>
       </c>
       <c r="E38" s="112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="128" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="129"/>
       <c r="C39" s="5"/>
@@ -2333,12 +2331,12 @@
         <v>16986.78</v>
       </c>
       <c r="E39" s="112" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="197" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B40" s="129"/>
       <c r="C40" s="5"/>
@@ -2346,13 +2344,13 @@
         <v>42385.55</v>
       </c>
       <c r="E40" s="112" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F40" s="198"/>
     </row>
     <row r="41" spans="1:7" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="204" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B41" s="205"/>
       <c r="C41" s="5"/>
@@ -2360,14 +2358,14 @@
         <v>56875.79</v>
       </c>
       <c r="E41" s="112" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F41" s="198"/>
       <c r="G41" s="198"/>
     </row>
     <row r="42" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="204" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B42" s="205"/>
       <c r="C42" s="5"/>
@@ -2375,14 +2373,14 @@
         <v>320000</v>
       </c>
       <c r="E42" s="112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F42" s="198"/>
       <c r="G42" s="198"/>
     </row>
     <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="128" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B43" s="129"/>
       <c r="C43" s="5"/>
@@ -2390,7 +2388,7 @@
         <v>74600</v>
       </c>
       <c r="E43" s="112" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2416,7 +2414,7 @@
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="204" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B46" s="205"/>
       <c r="C46" s="39"/>
@@ -2424,10 +2422,10 @@
         <v>150000</v>
       </c>
       <c r="E46" s="134" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2460,7 +2458,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2469,7 +2467,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2499,7 +2497,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B54" s="22"/>
       <c r="C54" s="22"/>
@@ -2517,7 +2515,7 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="4"/>
@@ -2540,7 +2538,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B59" s="10"/>
       <c r="C59" s="11"/>
@@ -2589,7 +2587,7 @@
     <row r="66" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -2599,7 +2597,7 @@
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B69" s="8"/>
       <c r="C69" s="4"/>
@@ -2612,7 +2610,7 @@
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B71" s="72">
         <f>E56</f>
@@ -2621,7 +2619,7 @@
     </row>
     <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B72" s="72">
         <f>E56-E54</f>
@@ -2630,7 +2628,7 @@
     </row>
     <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B73" s="72">
         <f>E69-E67</f>
@@ -2639,7 +2637,7 @@
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B74" s="72">
         <f>E69</f>
@@ -2653,7 +2651,7 @@
     </row>
     <row r="77" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="93" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B77" s="147">
         <v>-672526.10000000033</v>
@@ -2663,7 +2661,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B78" s="98">
         <f>-B72</f>
@@ -2672,7 +2670,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B79" s="98">
         <f>B98</f>
@@ -2681,7 +2679,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B80" s="99">
         <f>PRORRATEO!G36-B88</f>
@@ -2690,7 +2688,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="41" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B81" s="99"/>
     </row>
@@ -2702,7 +2700,7 @@
     </row>
     <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="96" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B83" s="97">
         <f>SUM(B77:C82)</f>
@@ -2717,7 +2715,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="93" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B85" s="147">
         <v>2000000</v>
@@ -2727,7 +2725,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B86" s="98">
         <f>-B73</f>
@@ -2737,7 +2735,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B87" s="98">
         <f>B106</f>
@@ -2747,7 +2745,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B88" s="99">
         <v>0</v>
@@ -2762,7 +2760,7 @@
     </row>
     <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="96" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B90" s="97">
         <f>SUM(B85:C89)</f>
@@ -2915,7 +2913,7 @@
       <c r="C2" s="154"/>
       <c r="D2" s="155"/>
       <c r="E2" s="155" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F2" s="155"/>
       <c r="G2" s="156">
@@ -2925,7 +2923,7 @@
       <c r="I2" s="155"/>
       <c r="J2" s="157"/>
       <c r="K2" s="155" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L2" s="158">
         <v>2200000</v>
@@ -2957,7 +2955,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="225" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B4" s="226"/>
       <c r="C4" s="226"/>
@@ -3053,7 +3051,7 @@
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="236" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="237"/>
       <c r="C9" s="237"/>
@@ -3073,7 +3071,7 @@
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="238" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10" s="238"/>
       <c r="C10" s="238"/>
@@ -3118,16 +3116,16 @@
         <v>22</v>
       </c>
       <c r="J11" s="214" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K11" s="214" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="223" t="s">
         <v>96</v>
       </c>
-      <c r="L11" s="223" t="s">
-        <v>97</v>
-      </c>
       <c r="M11" s="214" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N11" s="45" t="s">
         <v>20</v>
@@ -3165,10 +3163,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="46" t="s">
         <v>29</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>30</v>
       </c>
       <c r="D13" s="46"/>
       <c r="E13" s="55">
@@ -3226,10 +3224,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="D14" s="47"/>
       <c r="E14" s="55">
@@ -3287,13 +3285,13 @@
         <v>3</v>
       </c>
       <c r="B15" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="46" t="s">
-        <v>34</v>
-      </c>
       <c r="D15" s="47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" s="55">
         <v>5.4</v>
@@ -3351,13 +3349,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="D16" s="47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E16" s="55">
         <v>6.6</v>
@@ -3415,13 +3413,13 @@
         <v>5</v>
       </c>
       <c r="B17" s="164" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="164" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="164" t="s">
-        <v>38</v>
-      </c>
       <c r="D17" s="164" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E17" s="165">
         <v>6.6</v>
@@ -3474,7 +3472,7 @@
         <v>0.05</v>
       </c>
       <c r="R17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3482,13 +3480,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="46" t="s">
-        <v>40</v>
-      </c>
       <c r="D18" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E18" s="55">
         <v>5.4</v>
@@ -3546,13 +3544,13 @@
         <v>7</v>
       </c>
       <c r="B19" s="183" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="183" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="183" t="s">
-        <v>42</v>
-      </c>
       <c r="D19" s="183" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="185">
         <v>5.4</v>
@@ -3607,13 +3605,13 @@
         <v>8</v>
       </c>
       <c r="B20" s="183" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="183" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="183" t="s">
-        <v>44</v>
-      </c>
       <c r="D20" s="184" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E20" s="185">
         <v>6.6</v>
@@ -3671,13 +3669,13 @@
         <v>9</v>
       </c>
       <c r="B21" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="46" t="s">
-        <v>46</v>
-      </c>
       <c r="D21" s="47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21" s="55">
         <v>6.6</v>
@@ -3735,13 +3733,13 @@
         <v>10</v>
       </c>
       <c r="B22" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="46" t="s">
-        <v>48</v>
-      </c>
       <c r="D22" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" s="55">
         <v>5.4</v>
@@ -3799,10 +3797,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="46" t="s">
         <v>49</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>50</v>
       </c>
       <c r="D23" s="47"/>
       <c r="E23" s="55">
@@ -3856,7 +3854,7 @@
         <v>0.10999999999999999</v>
       </c>
       <c r="R23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3864,13 +3862,13 @@
         <v>12</v>
       </c>
       <c r="B24" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="46" t="s">
-        <v>52</v>
-      </c>
       <c r="D24" s="47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" s="55">
         <v>6.6</v>
@@ -3928,13 +3926,13 @@
         <v>13</v>
       </c>
       <c r="B25" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="46" t="s">
-        <v>54</v>
-      </c>
       <c r="D25" s="47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25" s="55">
         <v>6.6</v>
@@ -3991,10 +3989,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="164" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="164" t="s">
         <v>55</v>
-      </c>
-      <c r="C26" s="164" t="s">
-        <v>56</v>
       </c>
       <c r="D26" s="182"/>
       <c r="E26" s="165">
@@ -4052,10 +4050,10 @@
         <v>15</v>
       </c>
       <c r="B27" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="46" t="s">
         <v>57</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>58</v>
       </c>
       <c r="D27" s="47"/>
       <c r="E27" s="55">
@@ -4114,13 +4112,13 @@
         <v>16</v>
       </c>
       <c r="B28" s="46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C28" s="46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E28" s="55">
         <v>0.7</v>
@@ -4178,10 +4176,10 @@
         <v>17</v>
       </c>
       <c r="B29" s="46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C29" s="46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" s="47"/>
       <c r="E29" s="55">
@@ -4240,10 +4238,10 @@
         <v>18</v>
       </c>
       <c r="B30" s="46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C30" s="46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="92"/>
       <c r="E30" s="55">
@@ -4302,10 +4300,10 @@
         <v>19</v>
       </c>
       <c r="B31" s="183" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="184"/>
       <c r="E31" s="185">
@@ -4361,13 +4359,13 @@
         <v>20</v>
       </c>
       <c r="B32" s="62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" s="46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E32" s="55">
         <v>0.6</v>
@@ -4422,13 +4420,13 @@
         <v>21</v>
       </c>
       <c r="B33" s="62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33" s="48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E33" s="55">
         <v>0.3</v>
@@ -4483,10 +4481,10 @@
         <v>22</v>
       </c>
       <c r="B34" s="63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34" s="46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34" s="47"/>
       <c r="E34" s="55">
@@ -4542,13 +4540,13 @@
         <v>23</v>
       </c>
       <c r="B35" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="65" t="s">
-        <v>67</v>
-      </c>
       <c r="D35" s="47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E35" s="55">
         <v>0.3</v>
@@ -4783,19 +4781,19 @@
   <sheetData>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="135" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="135" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="135" t="s">
-        <v>83</v>
-      </c>
       <c r="E3" s="137" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="179" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" s="242" t="s">
         <v>89</v>
-      </c>
-      <c r="G3" s="179" t="s">
-        <v>123</v>
-      </c>
-      <c r="I3" s="242" t="s">
-        <v>90</v>
       </c>
       <c r="J3" s="243"/>
     </row>
@@ -4812,7 +4810,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="135" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" s="139">
         <v>4843.2564768292677</v>
@@ -4832,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="135" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" s="139">
         <v>24102.857781768264</v>
@@ -4852,7 +4850,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="135" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7" s="139">
         <v>30937.92295115858</v>
@@ -4872,7 +4870,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="135" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="139">
         <v>2179.4654145731706</v>
@@ -4892,7 +4890,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="136" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" s="139">
         <v>2663.7910622560971</v>
@@ -4912,7 +4910,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="136" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" s="139">
         <v>2663.7910622560971</v>
@@ -4932,7 +4930,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="136" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11" s="139">
         <v>2179.4654145731706</v>
@@ -4952,7 +4950,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="136" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E12" s="139">
         <v>2179.4654145731706</v>
@@ -4972,7 +4970,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="135" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E13" s="139">
         <v>82372.476165914617</v>
@@ -4992,7 +4990,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="136" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E14" s="139">
         <v>2663.7910622560971</v>
@@ -5012,7 +5010,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="136" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E15" s="139">
         <v>2179.4654145731706</v>
@@ -5032,7 +5030,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="135" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" s="139">
         <v>2179.4654145731706</v>
@@ -5052,7 +5050,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="136" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E17" s="139">
         <v>2663.7910622560971</v>
@@ -5072,7 +5070,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="135" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18" s="139">
         <v>2663.7910622560971</v>
@@ -5092,7 +5090,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="136" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E19" s="139">
         <v>2179.4654145731706</v>
@@ -5117,7 +5115,7 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="172" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C21" s="172"/>
       <c r="D21" s="173"/>
@@ -5138,7 +5136,7 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="135" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" s="135">
         <v>1</v>
@@ -5158,7 +5156,7 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="135" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="135">
         <v>2</v>
@@ -5178,7 +5176,7 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="135" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" s="135">
         <v>3</v>
@@ -5198,7 +5196,7 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="135" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25" s="135">
         <v>4</v>
@@ -5218,7 +5216,7 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="135" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C26" s="135">
         <v>5</v>
@@ -5238,7 +5236,7 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="135" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" s="135">
         <v>6</v>
@@ -5258,7 +5256,7 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="135" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" s="135">
         <v>7</v>
@@ -5278,7 +5276,7 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="135" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C29" s="135">
         <v>8</v>
@@ -5298,7 +5296,7 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="177" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C30" s="178"/>
       <c r="D30" s="176"/>

--- a/2026/SALTA 1167/Febrero/SALTA1167-Febrero.xlsx
+++ b/2026/SALTA 1167/Febrero/SALTA1167-Febrero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FA8043-3133-4394-B44B-AD2EBF684BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F470831-11D6-46E2-930F-239BC7E0150C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="149">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1125,7 +1125,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1205,7 +1205,6 @@
     <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1381,9 +1380,6 @@
     <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1395,16 +1391,12 @@
     <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="12" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1435,7 +1427,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1456,18 +1447,27 @@
     <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1480,14 +1480,14 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1504,21 +1504,12 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1566,9 +1557,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2015,18 +2003,18 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="206" t="s">
+      <c r="B3" s="204" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="206"/>
-      <c r="D3" s="206"/>
-      <c r="E3" s="207"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="205"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="69" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="18"/>
@@ -2058,49 +2046,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="209" t="s">
+      <c r="B8" s="207" t="s">
         <v>129</v>
       </c>
-      <c r="C8" s="209"/>
+      <c r="C8" s="207"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="209"/>
-      <c r="C9" s="209"/>
+      <c r="B9" s="207"/>
+      <c r="C9" s="207"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="209"/>
-      <c r="C10" s="209"/>
+      <c r="B10" s="207"/>
+      <c r="C10" s="207"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="208" t="s">
+      <c r="A13" s="206" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="208"/>
-      <c r="C13" s="208"/>
-      <c r="D13" s="208"/>
-      <c r="E13" s="208"/>
+      <c r="B13" s="206"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="208"/>
-      <c r="B14" s="208"/>
-      <c r="C14" s="208"/>
-      <c r="D14" s="208"/>
-      <c r="E14" s="208"/>
+      <c r="A14" s="206"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="208"/>
-      <c r="B15" s="208"/>
-      <c r="C15" s="208"/>
-      <c r="D15" s="208"/>
-      <c r="E15" s="208"/>
+      <c r="A15" s="206"/>
+      <c r="B15" s="206"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="208"/>
-      <c r="B16" s="208"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="208"/>
-      <c r="E16" s="208"/>
+      <c r="A16" s="206"/>
+      <c r="B16" s="206"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2122,30 +2110,30 @@
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="102"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="101"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="204" t="s">
+      <c r="A22" s="197" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="205"/>
+      <c r="B22" s="198"/>
       <c r="C22" s="39"/>
-      <c r="D22" s="117">
+      <c r="D22" s="116">
         <v>473045</v>
       </c>
-      <c r="E22" s="110" t="s">
+      <c r="E22" s="109" t="s">
         <v>133</v>
       </c>
-      <c r="H22" s="91"/>
+      <c r="H22" s="90"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="204"/>
-      <c r="B23" s="205"/>
+      <c r="A23" s="197"/>
+      <c r="B23" s="198"/>
       <c r="C23" s="39"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="110"/>
-      <c r="H23" s="91"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="109"/>
+      <c r="H23" s="90"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
@@ -2153,8 +2141,8 @@
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="131">
+      <c r="D24" s="117"/>
+      <c r="E24" s="130">
         <f>SUM(D22:D23)</f>
         <v>473045</v>
       </c>
@@ -2165,19 +2153,19 @@
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="130"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="129"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="204" t="s">
+      <c r="A26" s="197" t="s">
         <v>124</v>
       </c>
-      <c r="B26" s="205"/>
+      <c r="B26" s="198"/>
       <c r="C26" s="41"/>
-      <c r="D26" s="181">
+      <c r="D26" s="177">
         <v>74584</v>
       </c>
-      <c r="E26" s="201" t="s">
+      <c r="E26" s="196" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2187,8 +2175,8 @@
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="103">
+      <c r="D27" s="117"/>
+      <c r="E27" s="102">
         <f>SUM(D26:D26)</f>
         <v>74584</v>
       </c>
@@ -2197,10 +2185,10 @@
       <c r="A28" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="105"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="120"/>
-      <c r="E28" s="106"/>
+      <c r="B28" s="104"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="105"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
@@ -2208,8 +2196,8 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="109"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -2217,10 +2205,10 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="111">
+      <c r="D30" s="110">
         <v>5432.38</v>
       </c>
-      <c r="E30" s="110" t="s">
+      <c r="E30" s="109" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2228,12 +2216,12 @@
       <c r="A31" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="127"/>
+      <c r="B31" s="126"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="111">
+      <c r="D31" s="110">
         <v>275382.28999999998</v>
       </c>
-      <c r="E31" s="110" t="s">
+      <c r="E31" s="109" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2243,23 +2231,23 @@
       </c>
       <c r="B32" s="203"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="111">
+      <c r="D32" s="110">
         <v>174848.74</v>
       </c>
-      <c r="E32" s="110" t="s">
+      <c r="E32" s="109" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="113" t="s">
+      <c r="A33" s="112" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="109"/>
+      <c r="B33" s="108"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="111">
+      <c r="D33" s="110">
         <v>22064.59</v>
       </c>
-      <c r="E33" s="110" t="s">
+      <c r="E33" s="109" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2269,8 +2257,8 @@
       </c>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
-      <c r="D34" s="121"/>
-      <c r="E34" s="104">
+      <c r="D34" s="120"/>
+      <c r="E34" s="103">
         <f>SUM(D29:D33)</f>
         <v>477728</v>
       </c>
@@ -2279,115 +2267,115 @@
       <c r="A35" s="25"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
-      <c r="D35" s="118"/>
-      <c r="E35" s="107"/>
+      <c r="D35" s="117"/>
+      <c r="E35" s="106"/>
     </row>
     <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="204" t="s">
+      <c r="A36" s="197" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="205"/>
+      <c r="B36" s="198"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="111">
+      <c r="D36" s="110">
         <v>75000</v>
       </c>
-      <c r="E36" s="112" t="s">
+      <c r="E36" s="111" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="128" t="s">
+      <c r="A37" s="127" t="s">
         <v>137</v>
       </c>
-      <c r="B37" s="129"/>
+      <c r="B37" s="128"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="76">
+      <c r="D37" s="75">
         <v>4800</v>
       </c>
-      <c r="E37" s="112" t="s">
+      <c r="E37" s="111" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="197" t="s">
+      <c r="A38" s="192" t="s">
         <v>142</v>
       </c>
-      <c r="B38" s="129"/>
+      <c r="B38" s="128"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="76">
+      <c r="D38" s="75">
         <v>24000</v>
       </c>
-      <c r="E38" s="112" t="s">
+      <c r="E38" s="111" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="128" t="s">
+      <c r="A39" s="127" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="129"/>
+      <c r="B39" s="128"/>
       <c r="C39" s="5"/>
-      <c r="D39" s="76">
+      <c r="D39" s="75">
         <v>16986.78</v>
       </c>
-      <c r="E39" s="112" t="s">
+      <c r="E39" s="111" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="197" t="s">
+      <c r="A40" s="192" t="s">
         <v>139</v>
       </c>
-      <c r="B40" s="129"/>
+      <c r="B40" s="128"/>
       <c r="C40" s="5"/>
-      <c r="D40" s="76">
+      <c r="D40" s="75">
         <v>42385.55</v>
       </c>
-      <c r="E40" s="112" t="s">
+      <c r="E40" s="111" t="s">
         <v>140</v>
       </c>
-      <c r="F40" s="198"/>
+      <c r="F40" s="193"/>
     </row>
     <row r="41" spans="1:7" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="204" t="s">
+      <c r="A41" s="197" t="s">
         <v>147</v>
       </c>
-      <c r="B41" s="205"/>
+      <c r="B41" s="198"/>
       <c r="C41" s="5"/>
-      <c r="D41" s="76">
+      <c r="D41" s="75">
         <v>56875.79</v>
       </c>
-      <c r="E41" s="112" t="s">
+      <c r="E41" s="111" t="s">
         <v>143</v>
       </c>
-      <c r="F41" s="198"/>
-      <c r="G41" s="198"/>
+      <c r="F41" s="193"/>
+      <c r="G41" s="193"/>
     </row>
     <row r="42" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="204" t="s">
+      <c r="A42" s="197" t="s">
         <v>144</v>
       </c>
-      <c r="B42" s="205"/>
+      <c r="B42" s="198"/>
       <c r="C42" s="5"/>
-      <c r="D42" s="76">
+      <c r="D42" s="75">
         <v>320000</v>
       </c>
-      <c r="E42" s="112" t="s">
+      <c r="E42" s="111" t="s">
         <v>145</v>
       </c>
-      <c r="F42" s="198"/>
-      <c r="G42" s="198"/>
+      <c r="F42" s="193"/>
+      <c r="G42" s="193"/>
     </row>
     <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="128" t="s">
+      <c r="A43" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="B43" s="129"/>
+      <c r="B43" s="128"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="117">
+      <c r="D43" s="116">
         <v>74600</v>
       </c>
-      <c r="E43" s="112" t="s">
+      <c r="E43" s="111" t="s">
         <v>136</v>
       </c>
     </row>
@@ -2398,7 +2386,7 @@
       <c r="B44" s="25"/>
       <c r="C44" s="25"/>
       <c r="D44" s="24"/>
-      <c r="E44" s="103">
+      <c r="E44" s="102">
         <f>SUM(D36:D43)</f>
         <v>614648.12</v>
       </c>
@@ -2409,19 +2397,19 @@
       </c>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
-      <c r="D45" s="116"/>
-      <c r="E45" s="102"/>
+      <c r="D45" s="115"/>
+      <c r="E45" s="101"/>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="204" t="s">
+      <c r="A46" s="197" t="s">
         <v>27</v>
       </c>
-      <c r="B46" s="205"/>
+      <c r="B46" s="198"/>
       <c r="C46" s="39"/>
-      <c r="D46" s="117">
+      <c r="D46" s="116">
         <v>150000</v>
       </c>
-      <c r="E46" s="134" t="s">
+      <c r="E46" s="133" t="s">
         <v>145</v>
       </c>
       <c r="G46" t="s">
@@ -2429,11 +2417,11 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="128"/>
-      <c r="B47" s="129"/>
+      <c r="A47" s="127"/>
+      <c r="B47" s="128"/>
       <c r="C47" s="39"/>
-      <c r="D47" s="144"/>
-      <c r="E47" s="134"/>
+      <c r="D47" s="143"/>
+      <c r="E47" s="133"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
@@ -2441,8 +2429,8 @@
       </c>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
-      <c r="D48" s="118"/>
-      <c r="E48" s="131">
+      <c r="D48" s="117"/>
+      <c r="E48" s="130">
         <f>SUM(D46:D47)</f>
         <v>150000</v>
       </c>
@@ -2453,8 +2441,8 @@
       </c>
       <c r="B49" s="49"/>
       <c r="C49" s="21"/>
-      <c r="D49" s="115"/>
-      <c r="E49" s="103"/>
+      <c r="D49" s="114"/>
+      <c r="E49" s="102"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
@@ -2462,8 +2450,8 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="111"/>
-      <c r="E50" s="108"/>
+      <c r="D50" s="110"/>
+      <c r="E50" s="107"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
@@ -2471,7 +2459,7 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="111">
+      <c r="D51" s="110">
         <v>21963.1</v>
       </c>
       <c r="E51" s="29"/>
@@ -2482,8 +2470,8 @@
       </c>
       <c r="B52" s="38"/>
       <c r="C52" s="38"/>
-      <c r="D52" s="78"/>
-      <c r="E52" s="132">
+      <c r="D52" s="77"/>
+      <c r="E52" s="131">
         <f>SUM(D50:D51)</f>
         <v>21963.1</v>
       </c>
@@ -2492,8 +2480,8 @@
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="73"/>
-      <c r="E53" s="79"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="78"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="22" t="s">
@@ -2501,16 +2489,16 @@
       </c>
       <c r="B54" s="22"/>
       <c r="C54" s="22"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="133">
+      <c r="D54" s="79"/>
+      <c r="E54" s="132">
         <f>2200000-1811968.22</f>
         <v>388031.78</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
-      <c r="D55" s="81"/>
-      <c r="E55" s="82"/>
+      <c r="D55" s="80"/>
+      <c r="E55" s="81"/>
       <c r="F55" s="31"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2519,22 +2507,22 @@
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="4"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="84">
+      <c r="D56" s="82"/>
+      <c r="E56" s="83">
         <f>(SUM(E21:E54))</f>
         <v>2200000</v>
       </c>
-      <c r="F56" s="101"/>
+      <c r="F56" s="100"/>
       <c r="G56" s="31"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D57" s="81"/>
-      <c r="E57" s="81"/>
+      <c r="D57" s="80"/>
+      <c r="E57" s="80"/>
     </row>
     <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D58" s="81"/>
-      <c r="E58" s="81"/>
-      <c r="H58" s="122"/>
+      <c r="D58" s="80"/>
+      <c r="E58" s="80"/>
+      <c r="H58" s="121"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
@@ -2542,22 +2530,22 @@
       </c>
       <c r="B59" s="10"/>
       <c r="C59" s="11"/>
-      <c r="D59" s="85"/>
-      <c r="E59" s="86"/>
+      <c r="D59" s="84"/>
+      <c r="E59" s="85"/>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="75"/>
-      <c r="B60" s="109"/>
+      <c r="A60" s="74"/>
+      <c r="B60" s="108"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="76"/>
-      <c r="E60" s="74"/>
+      <c r="D60" s="75"/>
+      <c r="E60" s="73"/>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="212"/>
-      <c r="B61" s="212"/>
+      <c r="A61" s="201"/>
+      <c r="B61" s="201"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="111"/>
-      <c r="E61" s="74"/>
+      <c r="D61" s="110"/>
+      <c r="E61" s="73"/>
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
@@ -2567,11 +2555,11 @@
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="75"/>
-      <c r="B63" s="77"/>
+      <c r="A63" s="74"/>
+      <c r="B63" s="76"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="76"/>
-      <c r="E63" s="74"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="73"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="36"/>
@@ -2592,7 +2580,7 @@
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
       <c r="D67" s="23"/>
-      <c r="E67" s="196"/>
+      <c r="E67" s="191"/>
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2609,37 +2597,37 @@
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="71" t="s">
+      <c r="A71" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="72">
+      <c r="B71" s="71">
         <f>E56</f>
         <v>2200000</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="71" t="s">
+      <c r="A72" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="B72" s="72">
+      <c r="B72" s="71">
         <f>E56-E54</f>
         <v>1811968.22</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="71" t="s">
+      <c r="A73" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="B73" s="72">
+      <c r="B73" s="71">
         <f>E69-E67</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="71" t="s">
+      <c r="A74" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="B74" s="72">
+      <c r="B74" s="71">
         <f>E69</f>
         <v>0</v>
       </c>
@@ -2650,10 +2638,10 @@
       <c r="C76" s="27"/>
     </row>
     <row r="77" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="93" t="s">
+      <c r="A77" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="B77" s="147">
+      <c r="B77" s="146">
         <v>-672526.10000000033</v>
       </c>
       <c r="C77" s="27"/>
@@ -2663,7 +2651,7 @@
       <c r="A78" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="B78" s="98">
+      <c r="B78" s="97">
         <f>-B72</f>
         <v>-1811968.22</v>
       </c>
@@ -2672,7 +2660,7 @@
       <c r="A79" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B79" s="98">
+      <c r="B79" s="97">
         <f>B98</f>
         <v>0</v>
       </c>
@@ -2681,7 +2669,7 @@
       <c r="A80" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="99">
+      <c r="B80" s="98">
         <f>PRORRATEO!G36-B88</f>
         <v>2003377.2999999993</v>
       </c>
@@ -2690,34 +2678,34 @@
       <c r="A81" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="B81" s="99"/>
+      <c r="B81" s="98"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="100" t="s">
+      <c r="A82" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="B82" s="123"/>
+      <c r="B82" s="122"/>
     </row>
     <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="96" t="s">
+      <c r="A83" s="95" t="s">
         <v>114</v>
       </c>
-      <c r="B83" s="97">
+      <c r="B83" s="96">
         <f>SUM(B77:C82)</f>
         <v>-481117.02000000095</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="94"/>
-      <c r="B84" s="94"/>
+      <c r="A84" s="93"/>
+      <c r="B84" s="93"/>
       <c r="D84" s="31"/>
       <c r="E84" s="30"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="93" t="s">
+      <c r="A85" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="B85" s="147">
+      <c r="B85" s="146">
         <v>2000000</v>
       </c>
       <c r="D85" s="30"/>
@@ -2727,7 +2715,7 @@
       <c r="A86" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="B86" s="98">
+      <c r="B86" s="97">
         <f>-B73</f>
         <v>0</v>
       </c>
@@ -2737,7 +2725,7 @@
       <c r="A87" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B87" s="98">
+      <c r="B87" s="97">
         <f>B106</f>
         <v>0</v>
       </c>
@@ -2747,66 +2735,66 @@
       <c r="A88" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B88" s="99">
-        <v>0</v>
-      </c>
-      <c r="D88" s="198"/>
+      <c r="B88" s="98">
+        <v>0</v>
+      </c>
+      <c r="D88" s="193"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="100" t="s">
+      <c r="A89" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="B89" s="123"/>
+      <c r="B89" s="122"/>
     </row>
     <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="96" t="s">
+      <c r="A90" s="95" t="s">
         <v>115</v>
       </c>
-      <c r="B90" s="97">
+      <c r="B90" s="96">
         <f>SUM(B85:C89)</f>
         <v>2000000</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="94"/>
-      <c r="B91" s="94"/>
+      <c r="A91" s="93"/>
+      <c r="B91" s="93"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="94"/>
-      <c r="B92" s="94"/>
+      <c r="A92" s="93"/>
+      <c r="B92" s="93"/>
     </row>
     <row r="93" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="211" t="s">
+      <c r="A94" s="200" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="211"/>
-      <c r="C94" s="211"/>
+      <c r="B94" s="200"/>
+      <c r="C94" s="200"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="211"/>
-      <c r="B95" s="211"/>
-      <c r="C95" s="211"/>
+      <c r="A95" s="200"/>
+      <c r="B95" s="200"/>
+      <c r="C95" s="200"/>
     </row>
     <row r="96" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="88"/>
+      <c r="A96" s="87"/>
       <c r="B96" s="26"/>
       <c r="C96" s="26">
         <v>40000</v>
       </c>
-      <c r="E96" s="101"/>
+      <c r="E96" s="100"/>
     </row>
     <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="88"/>
-      <c r="B97" s="90"/>
-      <c r="C97" s="87"/>
-      <c r="D97" s="101"/>
+      <c r="A97" s="87"/>
+      <c r="B97" s="89"/>
+      <c r="C97" s="86"/>
+      <c r="D97" s="100"/>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B98" s="89">
+      <c r="B98" s="88">
         <f>SUM(B96:B97)</f>
         <v>0</v>
       </c>
@@ -2816,35 +2804,42 @@
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="210"/>
-      <c r="B100" s="210"/>
-      <c r="C100" s="210"/>
-      <c r="D100" s="210"/>
-      <c r="E100" s="210"/>
+      <c r="A100" s="199"/>
+      <c r="B100" s="199"/>
+      <c r="C100" s="199"/>
+      <c r="D100" s="199"/>
+      <c r="E100" s="199"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="210"/>
-      <c r="B101" s="210"/>
-      <c r="C101" s="210"/>
-      <c r="D101" s="210"/>
-      <c r="E101" s="210"/>
+      <c r="A101" s="199"/>
+      <c r="B101" s="199"/>
+      <c r="C101" s="199"/>
+      <c r="D101" s="199"/>
+      <c r="E101" s="199"/>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="210"/>
-      <c r="B102" s="210"/>
-      <c r="C102" s="210"/>
-      <c r="D102" s="210"/>
-      <c r="E102" s="210"/>
+      <c r="A102" s="199"/>
+      <c r="B102" s="199"/>
+      <c r="C102" s="199"/>
+      <c r="D102" s="199"/>
+      <c r="E102" s="199"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="210"/>
-      <c r="B103" s="210"/>
-      <c r="C103" s="210"/>
-      <c r="D103" s="210"/>
-      <c r="E103" s="210"/>
+      <c r="A103" s="199"/>
+      <c r="B103" s="199"/>
+      <c r="C103" s="199"/>
+      <c r="D103" s="199"/>
+      <c r="E103" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A100:E103"/>
     <mergeCell ref="A94:C95"/>
@@ -2852,13 +2847,6 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A26:B26"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2868,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R44"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4.42578125" customWidth="1"/>
@@ -2879,286 +2867,272 @@
     <col min="7" max="7" width="12.42578125" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" customWidth="1"/>
     <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" customWidth="1"/>
-    <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148"/>
-      <c r="B1" s="149"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="213"/>
-      <c r="F1" s="213"/>
-      <c r="G1" s="213"/>
-      <c r="H1" s="213"/>
-      <c r="I1" s="213"/>
-      <c r="J1" s="213"/>
-      <c r="K1" s="213"/>
-      <c r="L1" s="213"/>
-      <c r="M1" s="213"/>
-      <c r="N1" s="213"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="151"/>
-    </row>
-    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="152"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155" t="s">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="147"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="150"/>
+    </row>
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="151"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="155"/>
-      <c r="G2" s="156">
-        <v>0</v>
-      </c>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="155" t="s">
+      <c r="F2" s="154"/>
+      <c r="G2" s="155">
+        <v>0</v>
+      </c>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="158">
+      <c r="K2" s="156">
         <v>2200000</v>
       </c>
-      <c r="M2" s="158"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="160"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="20"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="152"/>
-      <c r="B3" s="153"/>
-      <c r="C3" s="154"/>
-      <c r="D3" s="154"/>
-      <c r="E3" s="154"/>
-      <c r="F3" s="154"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="154"/>
-      <c r="L3" s="154"/>
-      <c r="M3" s="154"/>
-      <c r="N3" s="159"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="161"/>
-      <c r="Q3" s="20"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="225" t="s">
+      <c r="L2" s="156"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="20"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="151"/>
+      <c r="B3" s="152"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="153"/>
+      <c r="E3" s="153"/>
+      <c r="F3" s="153"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="153"/>
+      <c r="I3" s="153"/>
+      <c r="J3" s="153"/>
+      <c r="K3" s="153"/>
+      <c r="L3" s="153"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="158"/>
+      <c r="O3" s="159"/>
+      <c r="P3" s="20"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="220" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="226"/>
-      <c r="C4" s="226"/>
-      <c r="D4" s="226"/>
-      <c r="E4" s="226"/>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
-      <c r="H4" s="226"/>
-      <c r="I4" s="226"/>
-      <c r="J4" s="226"/>
-      <c r="K4" s="226"/>
-      <c r="L4" s="226"/>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="20"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="228"/>
-      <c r="B5" s="229"/>
-      <c r="C5" s="229"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="229"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="229"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="229"/>
-      <c r="K5" s="229"/>
-      <c r="L5" s="229"/>
-      <c r="M5" s="229"/>
-      <c r="N5" s="229"/>
-      <c r="O5" s="229"/>
-      <c r="P5" s="230"/>
-      <c r="Q5" s="20"/>
-    </row>
-    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="228"/>
-      <c r="B6" s="229"/>
-      <c r="C6" s="229"/>
-      <c r="D6" s="229"/>
-      <c r="E6" s="229"/>
-      <c r="F6" s="229"/>
-      <c r="G6" s="229"/>
-      <c r="H6" s="229"/>
-      <c r="I6" s="229"/>
-      <c r="J6" s="229"/>
-      <c r="K6" s="229"/>
-      <c r="L6" s="229"/>
-      <c r="M6" s="229"/>
-      <c r="N6" s="229"/>
-      <c r="O6" s="229"/>
-      <c r="P6" s="230"/>
-      <c r="Q6" s="20"/>
-    </row>
-    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="228"/>
-      <c r="B7" s="229"/>
-      <c r="C7" s="229"/>
-      <c r="D7" s="229"/>
-      <c r="E7" s="229"/>
-      <c r="F7" s="229"/>
-      <c r="G7" s="229"/>
-      <c r="H7" s="229"/>
-      <c r="I7" s="229"/>
-      <c r="J7" s="229"/>
-      <c r="K7" s="229"/>
-      <c r="L7" s="229"/>
-      <c r="M7" s="229"/>
-      <c r="N7" s="229"/>
-      <c r="O7" s="229"/>
-      <c r="P7" s="230"/>
-      <c r="Q7" s="20"/>
-    </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="231"/>
-      <c r="B8" s="232"/>
-      <c r="C8" s="232"/>
-      <c r="D8" s="232"/>
-      <c r="E8" s="232"/>
-      <c r="F8" s="232"/>
-      <c r="G8" s="232"/>
-      <c r="H8" s="232"/>
-      <c r="I8" s="232"/>
-      <c r="J8" s="232"/>
-      <c r="K8" s="232"/>
-      <c r="L8" s="232"/>
-      <c r="M8" s="232"/>
-      <c r="N8" s="232"/>
-      <c r="O8" s="232"/>
-      <c r="P8" s="233"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="236" t="s">
+      <c r="B4" s="221"/>
+      <c r="C4" s="221"/>
+      <c r="D4" s="221"/>
+      <c r="E4" s="221"/>
+      <c r="F4" s="221"/>
+      <c r="G4" s="221"/>
+      <c r="H4" s="221"/>
+      <c r="I4" s="221"/>
+      <c r="J4" s="221"/>
+      <c r="K4" s="221"/>
+      <c r="L4" s="221"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="222"/>
+      <c r="P4" s="20"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="223"/>
+      <c r="B5" s="224"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="224"/>
+      <c r="F5" s="224"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="224"/>
+      <c r="J5" s="224"/>
+      <c r="K5" s="224"/>
+      <c r="L5" s="224"/>
+      <c r="M5" s="224"/>
+      <c r="N5" s="224"/>
+      <c r="O5" s="225"/>
+      <c r="P5" s="20"/>
+    </row>
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="223"/>
+      <c r="B6" s="224"/>
+      <c r="C6" s="224"/>
+      <c r="D6" s="224"/>
+      <c r="E6" s="224"/>
+      <c r="F6" s="224"/>
+      <c r="G6" s="224"/>
+      <c r="H6" s="224"/>
+      <c r="I6" s="224"/>
+      <c r="J6" s="224"/>
+      <c r="K6" s="224"/>
+      <c r="L6" s="224"/>
+      <c r="M6" s="224"/>
+      <c r="N6" s="224"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="20"/>
+    </row>
+    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="223"/>
+      <c r="B7" s="224"/>
+      <c r="C7" s="224"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="224"/>
+      <c r="F7" s="224"/>
+      <c r="G7" s="224"/>
+      <c r="H7" s="224"/>
+      <c r="I7" s="224"/>
+      <c r="J7" s="224"/>
+      <c r="K7" s="224"/>
+      <c r="L7" s="224"/>
+      <c r="M7" s="224"/>
+      <c r="N7" s="224"/>
+      <c r="O7" s="225"/>
+      <c r="P7" s="20"/>
+    </row>
+    <row r="8" spans="1:16" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="226"/>
+      <c r="B8" s="227"/>
+      <c r="C8" s="227"/>
+      <c r="D8" s="227"/>
+      <c r="E8" s="227"/>
+      <c r="F8" s="227"/>
+      <c r="G8" s="227"/>
+      <c r="H8" s="227"/>
+      <c r="I8" s="227"/>
+      <c r="J8" s="227"/>
+      <c r="K8" s="227"/>
+      <c r="L8" s="227"/>
+      <c r="M8" s="227"/>
+      <c r="N8" s="227"/>
+      <c r="O8" s="228"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="231" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="237"/>
-      <c r="C9" s="237"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="237"/>
-      <c r="F9" s="237"/>
-      <c r="G9" s="237"/>
-      <c r="H9" s="237"/>
-      <c r="I9" s="237"/>
-      <c r="J9" s="237"/>
-      <c r="K9" s="237"/>
-      <c r="L9" s="237"/>
-      <c r="M9" s="237"/>
-      <c r="N9" s="237"/>
-      <c r="O9" s="237"/>
-      <c r="P9" s="237"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="238" t="s">
+      <c r="B9" s="232"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="232"/>
+      <c r="E9" s="232"/>
+      <c r="F9" s="232"/>
+      <c r="G9" s="232"/>
+      <c r="H9" s="232"/>
+      <c r="I9" s="232"/>
+      <c r="J9" s="232"/>
+      <c r="K9" s="232"/>
+      <c r="L9" s="232"/>
+      <c r="M9" s="232"/>
+      <c r="N9" s="232"/>
+      <c r="O9" s="232"/>
+    </row>
+    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="233" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="238"/>
-      <c r="C10" s="238"/>
-      <c r="D10" s="238"/>
-      <c r="E10" s="238"/>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
-      <c r="H10" s="238"/>
-      <c r="I10" s="238"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="238"/>
-      <c r="L10" s="238"/>
-      <c r="M10" s="238"/>
-      <c r="N10" s="238"/>
-      <c r="O10" s="238"/>
-      <c r="P10" s="238"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="218" t="s">
+      <c r="B10" s="233"/>
+      <c r="C10" s="233"/>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="233"/>
+      <c r="G10" s="233"/>
+      <c r="H10" s="233"/>
+      <c r="I10" s="233"/>
+      <c r="J10" s="233"/>
+      <c r="K10" s="233"/>
+      <c r="L10" s="233"/>
+      <c r="M10" s="233"/>
+      <c r="N10" s="233"/>
+      <c r="O10" s="233"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="124"/>
-      <c r="C11" s="218" t="s">
+      <c r="B11" s="123"/>
+      <c r="C11" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="218" t="s">
+      <c r="D11" s="208" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="218" t="s">
+      <c r="E11" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="214" t="s">
+      <c r="F11" s="212" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="218" t="s">
+      <c r="G11" s="208" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="220" t="s">
+      <c r="H11" s="216" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="214" t="s">
+      <c r="I11" s="212" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="214" t="s">
+      <c r="J11" s="212" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="218" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="212" t="s">
         <v>80</v>
       </c>
-      <c r="K11" s="214" t="s">
-        <v>95</v>
-      </c>
-      <c r="L11" s="223" t="s">
-        <v>96</v>
-      </c>
-      <c r="M11" s="214" t="s">
-        <v>80</v>
-      </c>
-      <c r="N11" s="45" t="s">
+      <c r="M11" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="216" t="s">
+      <c r="N11" s="214" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="234" t="s">
+      <c r="O11" s="229" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="219"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="219"/>
-      <c r="D12" s="239"/>
-      <c r="E12" s="219"/>
-      <c r="F12" s="215"/>
-      <c r="G12" s="219"/>
-      <c r="H12" s="221"/>
-      <c r="I12" s="215"/>
-      <c r="J12" s="222"/>
-      <c r="K12" s="215"/>
-      <c r="L12" s="224"/>
-      <c r="M12" s="215"/>
-      <c r="N12" s="43" t="str">
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="210"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="210"/>
+      <c r="D12" s="209"/>
+      <c r="E12" s="210"/>
+      <c r="F12" s="213"/>
+      <c r="G12" s="210"/>
+      <c r="H12" s="217"/>
+      <c r="I12" s="213"/>
+      <c r="J12" s="213"/>
+      <c r="K12" s="219"/>
+      <c r="L12" s="213"/>
+      <c r="M12" s="43" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="O12" s="217"/>
-      <c r="P12" s="235"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="215"/>
+      <c r="O12" s="230"/>
+    </row>
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="46">
         <v>1</v>
       </c>
@@ -3187,39 +3161,35 @@
         <f>IF(H13&gt;0,H13*3%,0)</f>
         <v>720.01050000000009</v>
       </c>
-      <c r="J13" s="59">
+      <c r="J13" s="113">
+        <f>K$2*E13/100</f>
+        <v>264000</v>
+      </c>
+      <c r="K13" s="113">
+        <f>G$2*E13/100</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="189">
         <f>EDESUR!I5</f>
         <v>0</v>
       </c>
-      <c r="K13" s="114">
-        <f>L$2*E13/100</f>
-        <v>264000</v>
-      </c>
-      <c r="L13" s="114">
-        <f>G$2*E13/100</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="194">
-        <f>EDESUR!I5</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="192">
-        <f>ROUND(SUM(H13:M13),0) + Q13</f>
+      <c r="M13" s="187">
+        <f>ROUND(SUM(H13:L13),0) + P13</f>
         <v>288720.01</v>
       </c>
+      <c r="N13" s="59">
+        <f>ROUND(M13*6% + M13,0) + P13</f>
+        <v>306043.01</v>
+      </c>
       <c r="O13" s="60">
-        <f>ROUND(N13*6% + N13,0) + Q13</f>
-        <v>306043.01</v>
-      </c>
-      <c r="P13" s="61">
-        <f>ROUND(N13*3%,0) + N13</f>
+        <f>ROUND(M13*3%,0) + M13</f>
         <v>297382.01</v>
       </c>
-      <c r="Q13" s="31">
+      <c r="P13" s="31">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="46">
         <v>2</v>
       </c>
@@ -3247,40 +3217,36 @@
         <f t="shared" ref="I14:I35" si="1">IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="59">
+      <c r="J14" s="113">
+        <f>K$2*E14/100</f>
+        <v>145200</v>
+      </c>
+      <c r="K14" s="113">
+        <f>G$2*E14/100</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="189">
         <f>EDESUR!I6</f>
         <v>24102.857781768264</v>
       </c>
-      <c r="K14" s="114">
-        <f t="shared" ref="K14:K35" si="2">L$2*E14/100</f>
-        <v>145200</v>
-      </c>
-      <c r="L14" s="114">
-        <f t="shared" ref="L14:L35" si="3">G$2*E14/100</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="194">
-        <f>EDESUR!I6</f>
-        <v>24102.857781768264</v>
-      </c>
-      <c r="N14" s="192">
-        <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>188572.02</v>
+      <c r="M14" s="187">
+        <f>ROUND(SUM(H14:L14),0) + P14</f>
+        <v>164469.01999999999</v>
+      </c>
+      <c r="N14" s="59">
+        <f t="shared" ref="N14:N30" si="2">ROUND(M14*6% + M14,0) + P14</f>
+        <v>174337.02</v>
       </c>
       <c r="O14" s="60">
-        <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>199886.02</v>
-      </c>
-      <c r="P14" s="61">
-        <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>194229.02</v>
-      </c>
-      <c r="Q14" s="31">
-        <f>Q13+0.01</f>
+        <f t="shared" ref="O14:O35" si="3">ROUND(M14*3%,0) + M14</f>
+        <v>169403.02</v>
+      </c>
+      <c r="P14" s="31">
+        <f>P13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="46">
         <v>3</v>
       </c>
@@ -3311,40 +3277,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="59">
+      <c r="J15" s="113">
+        <f>K$2*E15/100</f>
+        <v>118800</v>
+      </c>
+      <c r="K15" s="113">
+        <f>G$2*E15/100</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="189">
         <f>EDESUR!I7</f>
         <v>20750.545398450711</v>
       </c>
-      <c r="K15" s="114">
+      <c r="M15" s="187">
+        <f>ROUND(SUM(H15:L15),0) + P15</f>
+        <v>139551.03</v>
+      </c>
+      <c r="N15" s="59">
         <f t="shared" si="2"/>
-        <v>118800</v>
-      </c>
-      <c r="L15" s="114">
+        <v>147924.03</v>
+      </c>
+      <c r="O15" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="194">
-        <f>EDESUR!I7</f>
-        <v>20750.545398450711</v>
-      </c>
-      <c r="N15" s="192">
-        <f t="shared" si="4"/>
-        <v>160301.03</v>
-      </c>
-      <c r="O15" s="60">
-        <f t="shared" si="5"/>
-        <v>169919.03</v>
-      </c>
-      <c r="P15" s="61">
-        <f t="shared" si="6"/>
-        <v>165110.03</v>
-      </c>
-      <c r="Q15" s="31">
-        <f t="shared" ref="Q15:Q30" si="7">Q14+0.01</f>
+        <v>143738.03</v>
+      </c>
+      <c r="P15" s="31">
+        <f t="shared" ref="P15:P30" si="4">P14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="46">
         <v>4</v>
       </c>
@@ -3375,107 +3337,99 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="59">
-        <f>EDESUR!I8</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="114">
+      <c r="J16" s="113">
+        <f>K$2*E16/100</f>
+        <v>145200</v>
+      </c>
+      <c r="K16" s="113">
+        <f>G$2*E16/100</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="189">
+        <f>EDESUR!I9</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="187">
+        <f>ROUND(SUM(H16:L16),0) + P16</f>
+        <v>144840.04</v>
+      </c>
+      <c r="N16" s="59">
         <f t="shared" si="2"/>
+        <v>153530.04</v>
+      </c>
+      <c r="O16" s="60">
+        <f t="shared" si="3"/>
+        <v>149185.04</v>
+      </c>
+      <c r="P16" s="31">
+        <f t="shared" si="4"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="161">
+        <v>5</v>
+      </c>
+      <c r="B17" s="161" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="161" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="161" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="162">
+        <v>6.6</v>
+      </c>
+      <c r="F17" s="163">
+        <v>132000.04999999999</v>
+      </c>
+      <c r="G17" s="163">
+        <f t="shared" ref="G17:G18" si="5">F17</f>
+        <v>132000.04999999999</v>
+      </c>
+      <c r="H17" s="164">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="164">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="165">
+        <f>K$2*E17/100</f>
         <v>145200</v>
       </c>
-      <c r="L16" s="114">
+      <c r="K17" s="165">
+        <f>G$2*E17/100</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="190">
+        <f>EDESUR!I10</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="188">
+        <f>ROUND(SUM(H17:L17),0) + P17</f>
+        <v>145200.04999999999</v>
+      </c>
+      <c r="N17" s="166">
+        <f t="shared" si="2"/>
+        <v>153912.04999999999</v>
+      </c>
+      <c r="O17" s="167">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="194">
-        <f>EDESUR!I9</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="192">
+        <v>149556.04999999999</v>
+      </c>
+      <c r="P17" s="31">
         <f t="shared" si="4"/>
-        <v>144840.04</v>
-      </c>
-      <c r="O16" s="60">
-        <f t="shared" si="5"/>
-        <v>153530.04</v>
-      </c>
-      <c r="P16" s="61">
-        <f t="shared" si="6"/>
-        <v>149185.04</v>
-      </c>
-      <c r="Q16" s="31">
-        <f t="shared" si="7"/>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="164">
-        <v>5</v>
-      </c>
-      <c r="B17" s="164" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="164" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="164" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="165">
-        <v>6.6</v>
-      </c>
-      <c r="F17" s="166">
-        <v>132000.04999999999</v>
-      </c>
-      <c r="G17" s="166">
-        <f t="shared" ref="G17:G18" si="8">F17</f>
-        <v>132000.04999999999</v>
-      </c>
-      <c r="H17" s="167">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="167">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="168">
-        <f>EDESUR!I9</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="169">
-        <f t="shared" si="2"/>
-        <v>145200</v>
-      </c>
-      <c r="L17" s="169">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="195">
-        <f>EDESUR!I10</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="193">
-        <f t="shared" si="4"/>
-        <v>145200.04999999999</v>
-      </c>
-      <c r="O17" s="170">
-        <f t="shared" si="5"/>
-        <v>153912.04999999999</v>
-      </c>
-      <c r="P17" s="171">
-        <f t="shared" si="6"/>
-        <v>149556.04999999999</v>
-      </c>
-      <c r="Q17" s="31">
-        <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
-      <c r="R17" t="s">
+      <c r="Q17" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="46">
         <v>6</v>
       </c>
@@ -3495,7 +3449,7 @@
         <v>108000.06</v>
       </c>
       <c r="G18" s="57">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>108000.06</v>
       </c>
       <c r="H18" s="58">
@@ -3506,114 +3460,106 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="59">
-        <f>EDESUR!I10</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="114">
+      <c r="J18" s="113">
+        <f>K$2*E18/100</f>
+        <v>118800</v>
+      </c>
+      <c r="K18" s="113">
+        <f>G$2*E18/100</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="189">
+        <f>EDESUR!I11</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="187">
+        <f>ROUND(SUM(H18:L18),0) + P18</f>
+        <v>118800.06</v>
+      </c>
+      <c r="N18" s="59">
         <f t="shared" si="2"/>
-        <v>118800</v>
-      </c>
-      <c r="L18" s="114">
+        <v>125928.06</v>
+      </c>
+      <c r="O18" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="194">
-        <f>EDESUR!I11</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="192">
+        <v>122364.06</v>
+      </c>
+      <c r="P18" s="31">
         <f t="shared" si="4"/>
-        <v>118800.06</v>
-      </c>
-      <c r="O18" s="60">
-        <f t="shared" si="5"/>
-        <v>125928.06</v>
-      </c>
-      <c r="P18" s="61">
-        <f t="shared" si="6"/>
-        <v>122364.06</v>
-      </c>
-      <c r="Q18" s="31">
-        <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="183">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="179">
         <v>7</v>
       </c>
-      <c r="B19" s="183" t="s">
+      <c r="B19" s="179" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="183" t="s">
+      <c r="C19" s="179" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="183" t="s">
+      <c r="D19" s="179" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="185">
+      <c r="E19" s="181">
         <v>5.4</v>
       </c>
       <c r="F19" s="57">
         <v>219240.07</v>
       </c>
       <c r="G19" s="57"/>
-      <c r="H19" s="186">
+      <c r="H19" s="182">
         <f t="shared" si="0"/>
         <v>219240.07</v>
       </c>
-      <c r="I19" s="186">
+      <c r="I19" s="182">
         <f t="shared" si="1"/>
         <v>6577.2020999999995</v>
       </c>
-      <c r="J19" s="187">
-        <f>EDESUR!I11</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="188">
+      <c r="J19" s="183">
+        <f>K$2*E19/100</f>
+        <v>118800</v>
+      </c>
+      <c r="K19" s="183">
+        <f>G$2*E19/100</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="189">
+        <f>EDESUR!I12</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="187">
+        <f>ROUND(SUM(H19:L19),0) + P19</f>
+        <v>344617.07</v>
+      </c>
+      <c r="N19" s="184">
         <f t="shared" si="2"/>
-        <v>118800</v>
-      </c>
-      <c r="L19" s="188">
+        <v>365294.07</v>
+      </c>
+      <c r="O19" s="185">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="194">
-        <f>EDESUR!I12</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="192">
+        <v>354956.07</v>
+      </c>
+      <c r="P19" s="31">
         <f t="shared" si="4"/>
-        <v>344617.07</v>
-      </c>
-      <c r="O19" s="189">
-        <f t="shared" si="5"/>
-        <v>365294.07</v>
-      </c>
-      <c r="P19" s="190">
-        <f t="shared" si="6"/>
-        <v>354956.07</v>
-      </c>
-      <c r="Q19" s="31">
-        <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="183">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="179">
         <v>8</v>
       </c>
-      <c r="B20" s="183" t="s">
+      <c r="B20" s="179" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="183" t="s">
+      <c r="C20" s="179" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="184" t="s">
+      <c r="D20" s="180" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="185">
+      <c r="E20" s="181">
         <v>6.6</v>
       </c>
       <c r="F20" s="57">
@@ -3623,48 +3569,44 @@
         <f>F20</f>
         <v>135960.07999999999</v>
       </c>
-      <c r="H20" s="186">
+      <c r="H20" s="182">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="186">
+      <c r="I20" s="182">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="187">
-        <f>EDESUR!I12</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="188">
-        <f t="shared" si="2"/>
+      <c r="J20" s="183">
+        <f>K$2*E20/100</f>
         <v>145200</v>
       </c>
-      <c r="L20" s="188">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="194">
+      <c r="K20" s="183">
+        <f>G$2*E20/100</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="189">
         <f>EDESUR!I13</f>
         <v>43777.036573498022</v>
       </c>
-      <c r="N20" s="192">
+      <c r="M20" s="187">
+        <f>ROUND(SUM(H20:L20),0) + P20</f>
+        <v>188977.08</v>
+      </c>
+      <c r="N20" s="184">
+        <f t="shared" si="2"/>
+        <v>200316.08</v>
+      </c>
+      <c r="O20" s="185">
+        <f t="shared" si="3"/>
+        <v>194646.08</v>
+      </c>
+      <c r="P20" s="31">
         <f t="shared" si="4"/>
-        <v>188977.08</v>
-      </c>
-      <c r="O20" s="189">
-        <f t="shared" si="5"/>
-        <v>200316.08</v>
-      </c>
-      <c r="P20" s="190">
-        <f t="shared" si="6"/>
-        <v>194646.08</v>
-      </c>
-      <c r="Q20" s="31">
-        <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="46">
         <v>9</v>
       </c>
@@ -3695,40 +3637,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="59">
-        <f>EDESUR!I13</f>
-        <v>43777.036573498022</v>
-      </c>
-      <c r="K21" s="114">
+      <c r="J21" s="113">
+        <f>K$2*E21/100</f>
+        <v>145200</v>
+      </c>
+      <c r="K21" s="113">
+        <f>G$2*E21/100</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="189">
+        <f>EDESUR!I14</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="187">
+        <f>ROUND(SUM(H21:L21),0) + P21</f>
+        <v>145200.09</v>
+      </c>
+      <c r="N21" s="59">
         <f t="shared" si="2"/>
-        <v>145200</v>
-      </c>
-      <c r="L21" s="114">
+        <v>153912.09</v>
+      </c>
+      <c r="O21" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="194">
-        <f>EDESUR!I14</f>
-        <v>0</v>
-      </c>
-      <c r="N21" s="192">
+        <v>149556.09</v>
+      </c>
+      <c r="P21" s="31">
         <f t="shared" si="4"/>
-        <v>188977.09</v>
-      </c>
-      <c r="O21" s="60">
-        <f t="shared" si="5"/>
-        <v>200316.09</v>
-      </c>
-      <c r="P21" s="61">
-        <f t="shared" si="6"/>
-        <v>194646.09</v>
-      </c>
-      <c r="Q21" s="31">
-        <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="46">
         <v>10</v>
       </c>
@@ -3759,40 +3697,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="59">
-        <f>EDESUR!I14</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="114">
+      <c r="J22" s="113">
+        <f>K$2*E22/100</f>
+        <v>118800</v>
+      </c>
+      <c r="K22" s="113">
+        <f>G$2*E22/100</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="189">
+        <f>EDESUR!I15</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="187">
+        <f>ROUND(SUM(H22:L22),0) + P22</f>
+        <v>2552.1</v>
+      </c>
+      <c r="N22" s="59">
         <f t="shared" si="2"/>
-        <v>118800</v>
-      </c>
-      <c r="L22" s="114">
+        <v>2705.1</v>
+      </c>
+      <c r="O22" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="194">
-        <f>EDESUR!I15</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="192">
+        <v>2629.1</v>
+      </c>
+      <c r="P22" s="31">
         <f t="shared" si="4"/>
-        <v>2552.1</v>
-      </c>
-      <c r="O22" s="60">
-        <f t="shared" si="5"/>
-        <v>2705.1</v>
-      </c>
-      <c r="P22" s="61">
-        <f t="shared" si="6"/>
-        <v>2629.1</v>
-      </c>
-      <c r="Q22" s="31">
-        <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="46">
         <v>11</v>
       </c>
@@ -3821,43 +3755,39 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J23" s="59">
-        <f>EDESUR!I15</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="114">
+      <c r="J23" s="113">
+        <f>K$2*E23/100</f>
+        <v>118800</v>
+      </c>
+      <c r="K23" s="113">
+        <f>G$2*E23/100</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="189">
+        <f>EDESUR!I12</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="187">
+        <f>ROUND(SUM(H23:L23),0) + P23</f>
+        <v>118800.11</v>
+      </c>
+      <c r="N23" s="59">
         <f t="shared" si="2"/>
-        <v>118800</v>
-      </c>
-      <c r="L23" s="114">
+        <v>125928.11</v>
+      </c>
+      <c r="O23" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="194">
-        <f>EDESUR!I12</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="192">
+        <v>122364.11</v>
+      </c>
+      <c r="P23" s="31">
         <f t="shared" si="4"/>
-        <v>118800.11</v>
-      </c>
-      <c r="O23" s="60">
-        <f t="shared" si="5"/>
-        <v>125928.11</v>
-      </c>
-      <c r="P23" s="61">
-        <f t="shared" si="6"/>
-        <v>122364.11</v>
-      </c>
-      <c r="Q23" s="31">
-        <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
-      <c r="R23" t="s">
+      <c r="Q23" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="46">
         <v>12</v>
       </c>
@@ -3888,40 +3818,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J24" s="59">
-        <f>EDESUR!I16</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="114">
+      <c r="J24" s="113">
+        <f>K$2*E24/100</f>
+        <v>145200</v>
+      </c>
+      <c r="K24" s="113">
+        <f>G$2*E24/100</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="189">
+        <f>EDESUR!I17</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="187">
+        <f>ROUND(SUM(H24:L24),0) + P24</f>
+        <v>145200.12</v>
+      </c>
+      <c r="N24" s="59">
         <f t="shared" si="2"/>
-        <v>145200</v>
-      </c>
-      <c r="L24" s="114">
+        <v>153912.12</v>
+      </c>
+      <c r="O24" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="194">
-        <f>EDESUR!I17</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="192">
+        <v>149556.12</v>
+      </c>
+      <c r="P24" s="31">
         <f t="shared" si="4"/>
-        <v>145200.12</v>
-      </c>
-      <c r="O24" s="60">
-        <f t="shared" si="5"/>
-        <v>153912.12</v>
-      </c>
-      <c r="P24" s="61">
-        <f t="shared" si="6"/>
-        <v>149556.12</v>
-      </c>
-      <c r="Q24" s="31">
-        <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="46">
         <v>13</v>
       </c>
@@ -3951,101 +3877,93 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J25" s="59">
-        <f>EDESUR!I17</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="114">
+      <c r="J25" s="113">
+        <f>K$2*E25/100</f>
+        <v>145200</v>
+      </c>
+      <c r="K25" s="113">
+        <f>G$2*E25/100</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="189">
+        <f>EDESUR!I18</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="187">
+        <f>ROUND(SUM(H25:L25),0) + P25</f>
+        <v>141355.13</v>
+      </c>
+      <c r="N25" s="59">
         <f t="shared" si="2"/>
-        <v>145200</v>
-      </c>
-      <c r="L25" s="114">
+        <v>149836.13</v>
+      </c>
+      <c r="O25" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="194">
-        <f>EDESUR!I18</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="192">
+        <v>145596.13</v>
+      </c>
+      <c r="P25" s="31">
         <f t="shared" si="4"/>
-        <v>141355.13</v>
-      </c>
-      <c r="O25" s="60">
-        <f t="shared" si="5"/>
-        <v>149836.13</v>
-      </c>
-      <c r="P25" s="61">
-        <f t="shared" si="6"/>
-        <v>145596.13</v>
-      </c>
-      <c r="Q25" s="31">
-        <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="164">
+    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="161">
         <v>14</v>
       </c>
-      <c r="B26" s="164" t="s">
+      <c r="B26" s="161" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="164" t="s">
+      <c r="C26" s="161" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="182"/>
-      <c r="E26" s="165">
+      <c r="D26" s="178"/>
+      <c r="E26" s="162">
         <v>5.4</v>
       </c>
-      <c r="F26" s="166">
+      <c r="F26" s="163">
         <v>108000.14</v>
       </c>
-      <c r="G26" s="166">
+      <c r="G26" s="163">
         <v>100000</v>
       </c>
-      <c r="H26" s="167">
+      <c r="H26" s="164">
         <f t="shared" si="0"/>
         <v>8000.1399999999994</v>
       </c>
-      <c r="I26" s="167">
+      <c r="I26" s="164">
         <f t="shared" si="1"/>
         <v>240.00419999999997</v>
       </c>
-      <c r="J26" s="168">
-        <f>EDESUR!I18</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="169">
+      <c r="J26" s="165">
+        <f>K$2*E26/100</f>
+        <v>118800</v>
+      </c>
+      <c r="K26" s="165">
+        <f>G$2*E26/100</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="190">
+        <f>EDESUR!I19</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="188">
+        <f>ROUND(SUM(H26:L26),0) + P26</f>
+        <v>127040.14</v>
+      </c>
+      <c r="N26" s="59">
         <f t="shared" si="2"/>
-        <v>118800</v>
-      </c>
-      <c r="L26" s="169">
+        <v>134663.14000000001</v>
+      </c>
+      <c r="O26" s="167">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="195">
-        <f>EDESUR!I19</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="193">
+        <v>130851.14</v>
+      </c>
+      <c r="P26" s="31">
         <f t="shared" si="4"/>
-        <v>127040.14</v>
-      </c>
-      <c r="O26" s="60">
-        <f t="shared" si="5"/>
-        <v>134663.14000000001</v>
-      </c>
-      <c r="P26" s="171">
-        <f t="shared" si="6"/>
-        <v>130851.14</v>
-      </c>
-      <c r="Q26" s="31">
-        <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="46">
         <v>15</v>
       </c>
@@ -4063,7 +3981,7 @@
         <v>108000.15</v>
       </c>
       <c r="G27" s="57">
-        <f t="shared" ref="G27:G35" si="9">F27</f>
+        <f t="shared" ref="G27:G35" si="6">F27</f>
         <v>108000.15</v>
       </c>
       <c r="H27" s="58">
@@ -4074,40 +3992,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J27" s="59">
-        <f>EDESUR!I19</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="114">
+      <c r="J27" s="113">
+        <f>K$2*E27/100</f>
+        <v>118800</v>
+      </c>
+      <c r="K27" s="113">
+        <f>G$2*E27/100</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="189">
+        <f>EDESUR!I16</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="187">
+        <f>ROUND(SUM(H27:L27),0) + P27</f>
+        <v>118800.15</v>
+      </c>
+      <c r="N27" s="59">
         <f t="shared" si="2"/>
-        <v>118800</v>
-      </c>
-      <c r="L27" s="114">
+        <v>125928.15</v>
+      </c>
+      <c r="O27" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="194">
-        <f>EDESUR!I16</f>
-        <v>0</v>
-      </c>
-      <c r="N27" s="192">
+        <v>122364.15</v>
+      </c>
+      <c r="P27" s="31">
         <f t="shared" si="4"/>
-        <v>118800.15</v>
-      </c>
-      <c r="O27" s="60">
-        <f t="shared" si="5"/>
-        <v>125928.15</v>
-      </c>
-      <c r="P27" s="61">
-        <f t="shared" si="6"/>
-        <v>122364.15</v>
-      </c>
-      <c r="Q27" s="31">
-        <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="46">
         <v>16</v>
       </c>
@@ -4127,7 +4041,7 @@
         <v>14000.16</v>
       </c>
       <c r="G28" s="57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>14000.16</v>
       </c>
       <c r="H28" s="58">
@@ -4138,40 +4052,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J28" s="59">
+      <c r="J28" s="113">
+        <f>K$2*E28/100</f>
+        <v>15400</v>
+      </c>
+      <c r="K28" s="113">
+        <f>G$2*E28/100</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="189">
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="K28" s="114">
+      <c r="M28" s="187">
+        <f>ROUND(SUM(H28:L28),0) + P28</f>
+        <v>15400.16</v>
+      </c>
+      <c r="N28" s="59">
         <f t="shared" si="2"/>
-        <v>15400</v>
-      </c>
-      <c r="L28" s="114">
+        <v>16324.16</v>
+      </c>
+      <c r="O28" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="194">
-        <f>EDESUR!I22</f>
-        <v>0</v>
-      </c>
-      <c r="N28" s="192">
+        <v>15862.16</v>
+      </c>
+      <c r="P28" s="31">
         <f t="shared" si="4"/>
-        <v>15400.16</v>
-      </c>
-      <c r="O28" s="60">
-        <f t="shared" si="5"/>
-        <v>16324.16</v>
-      </c>
-      <c r="P28" s="61">
-        <f t="shared" si="6"/>
-        <v>15862.16</v>
-      </c>
-      <c r="Q28" s="31">
-        <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="46">
         <v>17</v>
       </c>
@@ -4189,7 +4099,7 @@
         <v>12000.17</v>
       </c>
       <c r="G29" s="57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>12000.17</v>
       </c>
       <c r="H29" s="58">
@@ -4200,40 +4110,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J29" s="59">
-        <f>EDESUR!I21</f>
-        <v>88630.439753716972</v>
-      </c>
-      <c r="K29" s="114">
+      <c r="J29" s="113">
+        <f>K$2*E29/100</f>
+        <v>13200</v>
+      </c>
+      <c r="K29" s="113">
+        <f>G$2*E29/100</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="189">
+        <f>EDESUR!I23</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="187">
+        <f>ROUND(SUM(H29:L29),0) + P29</f>
+        <v>13200.17</v>
+      </c>
+      <c r="N29" s="59">
         <f t="shared" si="2"/>
-        <v>13200</v>
-      </c>
-      <c r="L29" s="114">
+        <v>13992.17</v>
+      </c>
+      <c r="O29" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="194">
-        <f>EDESUR!I23</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="192">
+        <v>13596.17</v>
+      </c>
+      <c r="P29" s="31">
         <f t="shared" si="4"/>
-        <v>101830.17</v>
-      </c>
-      <c r="O29" s="60">
-        <f t="shared" si="5"/>
-        <v>107940.17</v>
-      </c>
-      <c r="P29" s="61">
-        <f t="shared" si="6"/>
-        <v>104885.17</v>
-      </c>
-      <c r="Q29" s="31">
-        <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="46">
         <v>18</v>
       </c>
@@ -4243,7 +4149,7 @@
       <c r="C30" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="92"/>
+      <c r="D30" s="91"/>
       <c r="E30" s="55">
         <v>0.6</v>
       </c>
@@ -4251,7 +4157,7 @@
         <v>12000.18</v>
       </c>
       <c r="G30" s="57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>12000.18</v>
       </c>
       <c r="H30" s="58">
@@ -4262,103 +4168,95 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J30" s="59">
-        <f>EDESUR!I22</f>
-        <v>0</v>
-      </c>
-      <c r="K30" s="114">
+      <c r="J30" s="113">
+        <f>K$2*E30/100</f>
+        <v>13200</v>
+      </c>
+      <c r="K30" s="113">
+        <f>G$2*E30/100</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="189">
+        <f>EDESUR!I24</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="187">
+        <f>ROUND(SUM(H30:L30),0) + P30</f>
+        <v>13200.18</v>
+      </c>
+      <c r="N30" s="59">
         <f t="shared" si="2"/>
-        <v>13200</v>
-      </c>
-      <c r="L30" s="114">
+        <v>13992.18</v>
+      </c>
+      <c r="O30" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="194">
-        <f>EDESUR!I24</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="192">
+        <v>13596.18</v>
+      </c>
+      <c r="P30" s="31">
         <f t="shared" si="4"/>
-        <v>13200.18</v>
-      </c>
-      <c r="O30" s="60">
-        <f t="shared" si="5"/>
-        <v>13992.18</v>
-      </c>
-      <c r="P30" s="61">
-        <f t="shared" si="6"/>
-        <v>13596.18</v>
-      </c>
-      <c r="Q30" s="31">
-        <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="183">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="179">
         <v>19</v>
       </c>
-      <c r="B31" s="183" t="s">
+      <c r="B31" s="179" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="183" t="s">
+      <c r="C31" s="179" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="184"/>
-      <c r="E31" s="185">
+      <c r="D31" s="180"/>
+      <c r="E31" s="181">
         <v>0.6</v>
       </c>
       <c r="F31" s="57">
         <v>11640.19</v>
       </c>
       <c r="G31" s="57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>11640.19</v>
       </c>
-      <c r="H31" s="186">
+      <c r="H31" s="182">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="186">
+      <c r="I31" s="182">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="187">
-        <f>EDESUR!I23</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="188">
-        <f t="shared" si="2"/>
+      <c r="J31" s="183">
+        <f>K$2*E31/100</f>
         <v>13200</v>
       </c>
-      <c r="L31" s="188">
+      <c r="K31" s="183">
+        <f>G$2*E31/100</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="194">
+        <f>EDESUR!I25</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="195">
+        <f>ROUND(SUM(H31:L31),0) + P31</f>
+        <v>13200.19</v>
+      </c>
+      <c r="N31" s="184"/>
+      <c r="O31" s="185">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M31" s="199">
-        <f>EDESUR!I25</f>
-        <v>0</v>
-      </c>
-      <c r="N31" s="200">
-        <f t="shared" si="4"/>
-        <v>13200.19</v>
-      </c>
-      <c r="O31" s="189"/>
-      <c r="P31" s="190">
-        <f t="shared" si="6"/>
         <v>13596.19</v>
       </c>
-      <c r="Q31" s="31">
-        <f>Q30+0.01</f>
+      <c r="P31" s="31">
+        <f>P30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="62">
+    <row r="32" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="61">
         <v>20</v>
       </c>
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="61" t="s">
         <v>62</v>
       </c>
       <c r="C32" s="46" t="s">
@@ -4370,11 +4268,11 @@
       <c r="E32" s="55">
         <v>0.6</v>
       </c>
-      <c r="F32" s="64">
+      <c r="F32" s="63">
         <v>12000.2</v>
       </c>
       <c r="G32" s="57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>12000.2</v>
       </c>
       <c r="H32" s="58">
@@ -4385,41 +4283,37 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J32" s="59">
-        <f>EDESUR!I24</f>
-        <v>0</v>
-      </c>
-      <c r="K32" s="114">
-        <f t="shared" si="2"/>
+      <c r="J32" s="113">
+        <f>K$2*E32/100</f>
         <v>13200</v>
       </c>
-      <c r="L32" s="114">
+      <c r="K32" s="113">
+        <f>G$2*E32/100</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="189">
+        <f>EDESUR!I26</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="187">
+        <f>ROUND(SUM(H32:L32),0) + P32</f>
+        <v>13200.2</v>
+      </c>
+      <c r="N32" s="59"/>
+      <c r="O32" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M32" s="194">
-        <f>EDESUR!I26</f>
-        <v>0</v>
-      </c>
-      <c r="N32" s="192">
-        <f t="shared" si="4"/>
-        <v>13200.2</v>
-      </c>
-      <c r="O32" s="60"/>
-      <c r="P32" s="61">
-        <f t="shared" si="6"/>
         <v>13596.2</v>
       </c>
-      <c r="Q32" s="31">
-        <f t="shared" ref="Q32:Q35" si="10">Q31+0.01</f>
+      <c r="P32" s="31">
+        <f t="shared" ref="P32:P35" si="7">P31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="62">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="61">
         <v>21</v>
       </c>
-      <c r="B33" s="62" t="s">
+      <c r="B33" s="61" t="s">
         <v>63</v>
       </c>
       <c r="C33" s="48" t="s">
@@ -4431,11 +4325,11 @@
       <c r="E33" s="55">
         <v>0.3</v>
       </c>
-      <c r="F33" s="64">
+      <c r="F33" s="63">
         <v>6000.21</v>
       </c>
       <c r="G33" s="57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>6000.21</v>
       </c>
       <c r="H33" s="58">
@@ -4446,41 +4340,37 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J33" s="59">
-        <f>EDESUR!I25</f>
-        <v>0</v>
-      </c>
-      <c r="K33" s="114">
-        <f t="shared" si="2"/>
+      <c r="J33" s="113">
+        <f>K$2*E33/100</f>
         <v>6600</v>
       </c>
-      <c r="L33" s="114">
+      <c r="K33" s="113">
+        <f>G$2*E33/100</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="189">
+        <f>EDESUR!I27</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="187">
+        <f>ROUND(SUM(H33:L33),0) + P33</f>
+        <v>6600.21</v>
+      </c>
+      <c r="N33" s="59"/>
+      <c r="O33" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M33" s="194">
-        <f>EDESUR!I27</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="192">
-        <f t="shared" si="4"/>
-        <v>6600.21</v>
-      </c>
-      <c r="O33" s="60"/>
-      <c r="P33" s="61">
-        <f t="shared" si="6"/>
         <v>6798.21</v>
       </c>
-      <c r="Q33" s="31">
-        <f t="shared" si="10"/>
+      <c r="P33" s="31">
+        <f t="shared" si="7"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="63">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="62">
         <v>22</v>
       </c>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="62" t="s">
         <v>64</v>
       </c>
       <c r="C34" s="46" t="s">
@@ -4490,11 +4380,11 @@
       <c r="E34" s="55">
         <v>0.3</v>
       </c>
-      <c r="F34" s="64">
+      <c r="F34" s="63">
         <v>6000.22</v>
       </c>
-      <c r="G34" s="180">
-        <f t="shared" si="9"/>
+      <c r="G34" s="176">
+        <f t="shared" si="6"/>
         <v>6000.22</v>
       </c>
       <c r="H34" s="58">
@@ -4505,44 +4395,40 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J34" s="59">
-        <f>EDESUR!I26</f>
-        <v>0</v>
-      </c>
-      <c r="K34" s="114">
-        <f t="shared" si="2"/>
+      <c r="J34" s="113">
+        <f>K$2*E34/100</f>
         <v>6600</v>
       </c>
-      <c r="L34" s="114">
+      <c r="K34" s="113">
+        <f>G$2*E34/100</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="189">
+        <f>EDESUR!I28</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="187">
+        <f>ROUND(SUM(H34:L34),0) + P34</f>
+        <v>6600.22</v>
+      </c>
+      <c r="N34" s="59"/>
+      <c r="O34" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="194">
-        <f>EDESUR!I28</f>
-        <v>0</v>
-      </c>
-      <c r="N34" s="192">
-        <f t="shared" si="4"/>
-        <v>6600.22</v>
-      </c>
-      <c r="O34" s="60"/>
-      <c r="P34" s="61">
-        <f t="shared" si="6"/>
         <v>6798.22</v>
       </c>
-      <c r="Q34" s="31">
-        <f t="shared" si="10"/>
+      <c r="P34" s="31">
+        <f t="shared" si="7"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="46">
         <v>23</v>
       </c>
-      <c r="B35" s="65" t="s">
+      <c r="B35" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="65" t="s">
+      <c r="C35" s="64" t="s">
         <v>66</v>
       </c>
       <c r="D35" s="47" t="s">
@@ -4551,11 +4437,11 @@
       <c r="E35" s="55">
         <v>0.3</v>
       </c>
-      <c r="F35" s="64">
+      <c r="F35" s="63">
         <v>6000.23</v>
       </c>
       <c r="G35" s="57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>6000.23</v>
       </c>
       <c r="H35" s="58">
@@ -4566,42 +4452,38 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J35" s="59">
-        <f>EDESUR!I27</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="114">
-        <f t="shared" si="2"/>
+      <c r="J35" s="113">
+        <f>K$2*E35/100</f>
         <v>6600</v>
       </c>
-      <c r="L35" s="114">
+      <c r="K35" s="113">
+        <f>G$2*E35/100</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="189">
+        <f>EDESUR!I29</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="187">
+        <f>ROUND(SUM(H35:L35),0) + P35</f>
+        <v>6600.23</v>
+      </c>
+      <c r="N35" s="65"/>
+      <c r="O35" s="60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M35" s="194">
-        <f>EDESUR!I29</f>
-        <v>0</v>
-      </c>
-      <c r="N35" s="192">
-        <f t="shared" si="4"/>
-        <v>6600.23</v>
-      </c>
-      <c r="O35" s="66"/>
-      <c r="P35" s="61">
-        <f t="shared" si="6"/>
         <v>6798.23</v>
       </c>
-      <c r="Q35" s="31">
-        <f t="shared" si="10"/>
+      <c r="P35" s="31">
+        <f t="shared" si="7"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="67"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="126">
+    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="66"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="125">
         <f>SUM(E13:E35)</f>
         <v>99.999999999999986</v>
       </c>
@@ -4618,148 +4500,137 @@
         <v>125953.46000000004</v>
       </c>
       <c r="I36" s="44">
-        <f t="shared" ref="I36:O36" si="11">SUM(I13:I35)</f>
+        <f t="shared" ref="I36:N36" si="8">SUM(I13:I35)</f>
         <v>7537.2168000000001</v>
       </c>
-      <c r="J36" s="44">
-        <f t="shared" si="11"/>
-        <v>177260.87950743397</v>
-      </c>
-      <c r="K36" s="95">
-        <f t="shared" si="11"/>
+      <c r="J36" s="94">
+        <f t="shared" si="8"/>
         <v>2200000</v>
       </c>
-      <c r="L36" s="44">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M36" s="191"/>
-      <c r="N36" s="69">
-        <f>SUM(N13:N35)</f>
-        <v>2599383.7600000012</v>
-      </c>
-      <c r="O36" s="69">
-        <f t="shared" si="11"/>
-        <v>2706373.7100000009</v>
-      </c>
-      <c r="P36" s="69">
-        <f>SUM(P13:P35)</f>
-        <v>2677365.7600000012</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K36" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="186"/>
+      <c r="M36" s="68">
+        <f>SUM(M13:M35)</f>
+        <v>2422123.7600000012</v>
+      </c>
+      <c r="N36" s="68">
+        <f t="shared" si="8"/>
+        <v>2518477.7100000009</v>
+      </c>
+      <c r="O36" s="68">
+        <f>SUM(O13:O35)</f>
+        <v>2494788.7600000012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="210" t="str">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="199" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="210"/>
-      <c r="E39" s="210"/>
-      <c r="F39" s="210"/>
-      <c r="G39" s="210"/>
-      <c r="H39" s="210"/>
-      <c r="I39" s="210"/>
-      <c r="J39" s="210"/>
-      <c r="K39" s="210"/>
-      <c r="L39" s="210"/>
-      <c r="M39" s="210"/>
-      <c r="N39" s="210"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="210"/>
-      <c r="D40" s="210"/>
-      <c r="E40" s="210"/>
-      <c r="F40" s="210"/>
-      <c r="G40" s="210"/>
-      <c r="H40" s="210"/>
-      <c r="I40" s="210"/>
-      <c r="J40" s="210"/>
-      <c r="K40" s="210"/>
-      <c r="L40" s="210"/>
-      <c r="M40" s="210"/>
-      <c r="N40" s="210"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="210"/>
-      <c r="D41" s="210"/>
-      <c r="E41" s="210"/>
-      <c r="F41" s="210"/>
-      <c r="G41" s="210"/>
-      <c r="H41" s="210"/>
-      <c r="I41" s="210"/>
-      <c r="J41" s="210"/>
-      <c r="K41" s="210"/>
-      <c r="L41" s="210"/>
-      <c r="M41" s="210"/>
-      <c r="N41" s="210"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="210"/>
-      <c r="D42" s="210"/>
-      <c r="E42" s="210"/>
-      <c r="F42" s="210"/>
-      <c r="G42" s="210"/>
-      <c r="H42" s="210"/>
-      <c r="I42" s="210"/>
-      <c r="J42" s="210"/>
-      <c r="K42" s="210"/>
-      <c r="L42" s="210"/>
-      <c r="M42" s="210"/>
-      <c r="N42" s="210"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="210"/>
-      <c r="D43" s="210"/>
-      <c r="E43" s="210"/>
-      <c r="F43" s="210"/>
-      <c r="G43" s="210"/>
-      <c r="H43" s="210"/>
-      <c r="I43" s="210"/>
-      <c r="J43" s="210"/>
-      <c r="K43" s="210"/>
-      <c r="L43" s="210"/>
-      <c r="M43" s="210"/>
-      <c r="N43" s="210"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="210"/>
-      <c r="D44" s="210"/>
-      <c r="E44" s="210"/>
-      <c r="F44" s="210"/>
-      <c r="G44" s="210"/>
-      <c r="H44" s="210"/>
-      <c r="I44" s="210"/>
-      <c r="J44" s="210"/>
-      <c r="K44" s="210"/>
-      <c r="L44" s="210"/>
-      <c r="M44" s="210"/>
-      <c r="N44" s="210"/>
+      <c r="D39" s="199"/>
+      <c r="E39" s="199"/>
+      <c r="F39" s="199"/>
+      <c r="G39" s="199"/>
+      <c r="H39" s="199"/>
+      <c r="I39" s="199"/>
+      <c r="J39" s="199"/>
+      <c r="K39" s="199"/>
+      <c r="L39" s="199"/>
+      <c r="M39" s="199"/>
+    </row>
+    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="199"/>
+      <c r="D40" s="199"/>
+      <c r="E40" s="199"/>
+      <c r="F40" s="199"/>
+      <c r="G40" s="199"/>
+      <c r="H40" s="199"/>
+      <c r="I40" s="199"/>
+      <c r="J40" s="199"/>
+      <c r="K40" s="199"/>
+      <c r="L40" s="199"/>
+      <c r="M40" s="199"/>
+    </row>
+    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="199"/>
+      <c r="D41" s="199"/>
+      <c r="E41" s="199"/>
+      <c r="F41" s="199"/>
+      <c r="G41" s="199"/>
+      <c r="H41" s="199"/>
+      <c r="I41" s="199"/>
+      <c r="J41" s="199"/>
+      <c r="K41" s="199"/>
+      <c r="L41" s="199"/>
+      <c r="M41" s="199"/>
+    </row>
+    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="199"/>
+      <c r="D42" s="199"/>
+      <c r="E42" s="199"/>
+      <c r="F42" s="199"/>
+      <c r="G42" s="199"/>
+      <c r="H42" s="199"/>
+      <c r="I42" s="199"/>
+      <c r="J42" s="199"/>
+      <c r="K42" s="199"/>
+      <c r="L42" s="199"/>
+      <c r="M42" s="199"/>
+    </row>
+    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="199"/>
+      <c r="D43" s="199"/>
+      <c r="E43" s="199"/>
+      <c r="F43" s="199"/>
+      <c r="G43" s="199"/>
+      <c r="H43" s="199"/>
+      <c r="I43" s="199"/>
+      <c r="J43" s="199"/>
+      <c r="K43" s="199"/>
+      <c r="L43" s="199"/>
+      <c r="M43" s="199"/>
+    </row>
+    <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="199"/>
+      <c r="D44" s="199"/>
+      <c r="E44" s="199"/>
+      <c r="F44" s="199"/>
+      <c r="G44" s="199"/>
+      <c r="H44" s="199"/>
+      <c r="I44" s="199"/>
+      <c r="J44" s="199"/>
+      <c r="K44" s="199"/>
+      <c r="L44" s="199"/>
+      <c r="M44" s="199"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="C39:N44"/>
+  <mergeCells count="18">
+    <mergeCell ref="E1:M1"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="A4:O8"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C39:M44"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A4:P8"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="A9:P9"/>
-    <mergeCell ref="A10:P10"/>
-    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4780,588 +4651,573 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="135" t="s">
+      <c r="B3" s="134" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="135" t="s">
+      <c r="C3" s="134" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="137" t="s">
+      <c r="E3" s="136" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="179" t="s">
+      <c r="G3" s="175" t="s">
         <v>122</v>
       </c>
-      <c r="I3" s="242" t="s">
+      <c r="I3" s="236" t="s">
         <v>89</v>
       </c>
-      <c r="J3" s="243"/>
+      <c r="J3" s="237"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="135"/>
-      <c r="C4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="G4" s="138"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="243"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="G4" s="137"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="237"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="135">
+      <c r="B5" s="134">
         <v>1</v>
       </c>
-      <c r="C5" s="135" t="s">
+      <c r="C5" s="134" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="139">
+      <c r="E5" s="138">
         <v>4843.2564768292677</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="140">
+      <c r="G5" s="139">
         <v>4843.2564768292677</v>
       </c>
-      <c r="I5" s="240">
+      <c r="I5" s="234">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="241"/>
+      <c r="J5" s="235"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="135">
+      <c r="B6" s="134">
         <v>1</v>
       </c>
-      <c r="C6" s="135" t="s">
+      <c r="C6" s="134" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="139">
+      <c r="E6" s="138">
         <v>24102.857781768264</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="140">
-        <v>0</v>
-      </c>
-      <c r="I6" s="240">
+      <c r="G6" s="139">
+        <v>0</v>
+      </c>
+      <c r="I6" s="234">
         <f t="shared" ref="I6:I21" si="0">E6-G6</f>
         <v>24102.857781768264</v>
       </c>
-      <c r="J6" s="241"/>
+      <c r="J6" s="235"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="135">
+      <c r="B7" s="134">
         <v>1</v>
       </c>
-      <c r="C7" s="135" t="s">
+      <c r="C7" s="134" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="139">
+      <c r="E7" s="138">
         <v>30937.92295115858</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="140">
+      <c r="G7" s="139">
         <v>10187.377552707869</v>
       </c>
-      <c r="I7" s="240">
+      <c r="I7" s="234">
         <f t="shared" si="0"/>
         <v>20750.545398450711</v>
       </c>
-      <c r="J7" s="241"/>
+      <c r="J7" s="235"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="135">
+      <c r="B8" s="134">
         <v>2</v>
       </c>
-      <c r="C8" s="135" t="s">
+      <c r="C8" s="134" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="139">
+      <c r="E8" s="138">
         <v>2179.4654145731706</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="140">
+      <c r="G8" s="139">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I8" s="240">
+      <c r="I8" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="241"/>
+      <c r="J8" s="235"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="136">
+      <c r="B9" s="135">
         <v>2</v>
       </c>
-      <c r="C9" s="136" t="s">
+      <c r="C9" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="139">
+      <c r="E9" s="138">
         <v>2663.7910622560971</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="140">
+      <c r="G9" s="139">
         <v>2663.7910622560971</v>
       </c>
-      <c r="I9" s="240">
+      <c r="I9" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="241"/>
+      <c r="J9" s="235"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="136">
+      <c r="B10" s="135">
         <v>2</v>
       </c>
-      <c r="C10" s="136" t="s">
+      <c r="C10" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="139">
+      <c r="E10" s="138">
         <v>2663.7910622560971</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="140">
+      <c r="G10" s="139">
         <v>2663.7910622560971</v>
       </c>
-      <c r="I10" s="240">
+      <c r="I10" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="241"/>
+      <c r="J10" s="235"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="136">
+      <c r="B11" s="135">
         <v>2</v>
       </c>
-      <c r="C11" s="136" t="s">
+      <c r="C11" s="135" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="139">
+      <c r="E11" s="138">
         <v>2179.4654145731706</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="140">
+      <c r="G11" s="139">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I11" s="240">
+      <c r="I11" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="241"/>
+      <c r="J11" s="235"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="136">
+      <c r="B12" s="135">
         <v>3</v>
       </c>
-      <c r="C12" s="136" t="s">
+      <c r="C12" s="135" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="139">
+      <c r="E12" s="138">
         <v>2179.4654145731706</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="140">
+      <c r="G12" s="139">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I12" s="240">
+      <c r="I12" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="241"/>
+      <c r="J12" s="235"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="135">
+      <c r="B13" s="134">
         <v>3</v>
       </c>
-      <c r="C13" s="135" t="s">
+      <c r="C13" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="139">
+      <c r="E13" s="138">
         <v>82372.476165914617</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="140">
+      <c r="G13" s="139">
         <v>38595.439592416595</v>
       </c>
-      <c r="I13" s="240">
+      <c r="I13" s="234">
         <f t="shared" si="0"/>
         <v>43777.036573498022</v>
       </c>
-      <c r="J13" s="241"/>
+      <c r="J13" s="235"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="136">
+      <c r="B14" s="135">
         <v>3</v>
       </c>
-      <c r="C14" s="136" t="s">
+      <c r="C14" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="139">
+      <c r="E14" s="138">
         <v>2663.7910622560971</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="140">
+      <c r="G14" s="139">
         <v>2663.7910622560971</v>
       </c>
-      <c r="I14" s="240">
+      <c r="I14" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="241"/>
+      <c r="J14" s="235"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="136">
+      <c r="B15" s="135">
         <v>3</v>
       </c>
-      <c r="C15" s="136" t="s">
+      <c r="C15" s="135" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="139">
+      <c r="E15" s="138">
         <v>2179.4654145731706</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="140">
+      <c r="G15" s="139">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I15" s="240">
+      <c r="I15" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="241"/>
+      <c r="J15" s="235"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="135">
+      <c r="B16" s="134">
         <v>4</v>
       </c>
-      <c r="C16" s="135" t="s">
+      <c r="C16" s="134" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="139">
+      <c r="E16" s="138">
         <v>2179.4654145731706</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="140">
+      <c r="G16" s="139">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I16" s="240">
+      <c r="I16" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="241"/>
+      <c r="J16" s="235"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="136">
+      <c r="B17" s="135">
         <v>4</v>
       </c>
-      <c r="C17" s="136" t="s">
+      <c r="C17" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="139">
+      <c r="E17" s="138">
         <v>2663.7910622560971</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="140">
+      <c r="G17" s="139">
         <v>2663.7910622560971</v>
       </c>
-      <c r="I17" s="240">
+      <c r="I17" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="241"/>
+      <c r="J17" s="235"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="135">
+      <c r="B18" s="134">
         <v>4</v>
       </c>
-      <c r="C18" s="135" t="s">
+      <c r="C18" s="134" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="139">
+      <c r="E18" s="138">
         <v>2663.7910622560971</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="140">
+      <c r="G18" s="139">
         <v>2663.7910622560971</v>
       </c>
-      <c r="I18" s="240">
+      <c r="I18" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="241"/>
+      <c r="J18" s="235"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="136">
+      <c r="B19" s="135">
         <v>4</v>
       </c>
-      <c r="C19" s="136" t="s">
+      <c r="C19" s="135" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="139">
+      <c r="E19" s="138">
         <v>2179.4654145731706</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="140">
+      <c r="G19" s="139">
         <v>2179.4654145731706</v>
       </c>
-      <c r="I19" s="240">
+      <c r="I19" s="234">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="241"/>
+      <c r="J19" s="235"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="135"/>
-      <c r="C20" s="135"/>
-      <c r="E20" s="135"/>
-      <c r="G20" s="138"/>
-      <c r="I20" s="240"/>
-      <c r="J20" s="241"/>
+      <c r="B20" s="134"/>
+      <c r="C20" s="134"/>
+      <c r="E20" s="134"/>
+      <c r="G20" s="137"/>
+      <c r="I20" s="234"/>
+      <c r="J20" s="235"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="172" t="s">
+      <c r="B21" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="C21" s="172"/>
-      <c r="D21" s="173"/>
-      <c r="E21" s="174">
+      <c r="C21" s="168"/>
+      <c r="D21" s="169"/>
+      <c r="E21" s="170">
         <f>SUM(E5:E20)</f>
         <v>168652.26117439024</v>
       </c>
-      <c r="F21" s="175"/>
-      <c r="G21" s="174">
+      <c r="F21" s="171"/>
+      <c r="G21" s="170">
         <f>SUM(G5:G20)</f>
         <v>80021.821420673266</v>
       </c>
-      <c r="I21" s="240">
+      <c r="I21" s="234">
         <f t="shared" si="0"/>
         <v>88630.439753716972</v>
       </c>
-      <c r="J21" s="241"/>
+      <c r="J21" s="235"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="135" t="s">
+      <c r="B22" s="134" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="135">
+      <c r="C22" s="134">
         <v>1</v>
       </c>
-      <c r="E22" s="145">
+      <c r="E22" s="144">
         <v>282.5232944817073</v>
       </c>
-      <c r="G22" s="146">
+      <c r="G22" s="145">
         <f>E22</f>
         <v>282.5232944817073</v>
       </c>
-      <c r="I22" s="240">
+      <c r="I22" s="234">
         <f t="shared" ref="I22" si="1">E22-G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="241"/>
+      <c r="J22" s="235"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="135" t="s">
+      <c r="B23" s="134" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="135">
+      <c r="C23" s="134">
         <v>2</v>
       </c>
-      <c r="E23" s="145">
+      <c r="E23" s="144">
         <v>242.16282384146339</v>
       </c>
-      <c r="G23" s="146">
+      <c r="G23" s="145">
         <f t="shared" ref="G23:G29" si="2">E23</f>
         <v>242.16282384146339</v>
       </c>
-      <c r="I23" s="240">
+      <c r="I23" s="234">
         <f t="shared" ref="I23:I31" si="3">E23-G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="241"/>
+      <c r="J23" s="235"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="135" t="s">
+      <c r="B24" s="134" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="135">
+      <c r="C24" s="134">
         <v>3</v>
       </c>
-      <c r="E24" s="145">
+      <c r="E24" s="144">
         <v>242.16282384146339</v>
       </c>
-      <c r="G24" s="146">
+      <c r="G24" s="145">
         <f t="shared" si="2"/>
         <v>242.16282384146339</v>
       </c>
-      <c r="I24" s="240">
+      <c r="I24" s="234">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="241"/>
+      <c r="J24" s="235"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="135" t="s">
+      <c r="B25" s="134" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="135">
+      <c r="C25" s="134">
         <v>4</v>
       </c>
-      <c r="E25" s="145">
+      <c r="E25" s="144">
         <v>242.16282384146339</v>
       </c>
-      <c r="G25" s="146">
+      <c r="G25" s="145">
         <f t="shared" si="2"/>
         <v>242.16282384146339</v>
       </c>
-      <c r="I25" s="240">
+      <c r="I25" s="234">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="241"/>
+      <c r="J25" s="235"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="135" t="s">
+      <c r="B26" s="134" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="135">
+      <c r="C26" s="134">
         <v>5</v>
       </c>
-      <c r="E26" s="145">
+      <c r="E26" s="144">
         <v>242.16282384146339</v>
       </c>
-      <c r="G26" s="146">
+      <c r="G26" s="145">
         <f t="shared" si="2"/>
         <v>242.16282384146339</v>
       </c>
-      <c r="I26" s="240">
+      <c r="I26" s="234">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="241"/>
+      <c r="J26" s="235"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="135" t="s">
+      <c r="B27" s="134" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="135">
+      <c r="C27" s="134">
         <v>6</v>
       </c>
-      <c r="E27" s="145">
+      <c r="E27" s="144">
         <v>121.0814119207317</v>
       </c>
-      <c r="G27" s="146">
+      <c r="G27" s="145">
         <f t="shared" si="2"/>
         <v>121.0814119207317</v>
       </c>
-      <c r="I27" s="240">
+      <c r="I27" s="234">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J27" s="241"/>
+      <c r="J27" s="235"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="135" t="s">
+      <c r="B28" s="134" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="135">
+      <c r="C28" s="134">
         <v>7</v>
       </c>
-      <c r="E28" s="145">
+      <c r="E28" s="144">
         <v>121.0814119207317</v>
       </c>
-      <c r="G28" s="146">
+      <c r="G28" s="145">
         <f t="shared" si="2"/>
         <v>121.0814119207317</v>
       </c>
-      <c r="I28" s="240">
+      <c r="I28" s="234">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J28" s="241"/>
+      <c r="J28" s="235"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="135" t="s">
+      <c r="B29" s="134" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="135">
+      <c r="C29" s="134">
         <v>8</v>
       </c>
-      <c r="E29" s="145">
+      <c r="E29" s="144">
         <v>121.0814119207317</v>
       </c>
-      <c r="G29" s="146">
+      <c r="G29" s="145">
         <f t="shared" si="2"/>
         <v>121.0814119207317</v>
       </c>
-      <c r="I29" s="240">
+      <c r="I29" s="234">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="241"/>
+      <c r="J29" s="235"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="177" t="s">
+      <c r="B30" s="173" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="178"/>
-      <c r="D30" s="176"/>
-      <c r="E30" s="174">
+      <c r="C30" s="174"/>
+      <c r="D30" s="172"/>
+      <c r="E30" s="170">
         <f>SUM(E22:E29)</f>
         <v>1614.4188256097557</v>
       </c>
-      <c r="F30" s="176"/>
-      <c r="G30" s="174">
+      <c r="F30" s="172"/>
+      <c r="G30" s="170">
         <f>SUM(G22:G29)</f>
         <v>1614.4188256097557</v>
       </c>
-      <c r="I30" s="240">
+      <c r="I30" s="234">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="241"/>
+      <c r="J30" s="235"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E31" s="143"/>
-      <c r="G31" s="140"/>
-      <c r="I31" s="240">
+      <c r="E31" s="142"/>
+      <c r="G31" s="139"/>
+      <c r="I31" s="234">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="241"/>
+      <c r="J31" s="235"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E32" s="141"/>
-      <c r="G32" s="142"/>
-      <c r="I32" s="240"/>
-      <c r="J32" s="241"/>
+      <c r="E32" s="140"/>
+      <c r="G32" s="141"/>
+      <c r="I32" s="234"/>
+      <c r="J32" s="235"/>
     </row>
     <row r="33" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E33" s="143">
+      <c r="E33" s="142">
         <f>E30+E21</f>
         <v>170266.68</v>
       </c>
-      <c r="G33" s="140">
+      <c r="G33" s="139">
         <f>G21+G30</f>
         <v>81636.240246283021</v>
       </c>
-      <c r="I33" s="240">
+      <c r="I33" s="234">
         <f>E33-G33</f>
         <v>88630.439753716972</v>
       </c>
-      <c r="J33" s="241"/>
+      <c r="J33" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5378,6 +5234,21 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>
